--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_lastcheck.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_lastcheck.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,6 +146,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -155,16 +164,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -795,11 +798,11 @@
       <c r="G4" s="9" t="n">
         <v>12.1</v>
       </c>
-      <c r="H4" s="11" t="n">
-        <v>10.8</v>
+      <c r="H4" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>1.2</v>
@@ -807,50 +810,50 @@
       <c r="K4" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="L4" s="11" t="n">
+      <c r="L4" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="M4" s="13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="O4" s="3" t="n">
+      <c r="M4" s="9" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="N4" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="O4" s="9" t="n">
         <v>99</v>
       </c>
-      <c r="P4" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q4" s="3" t="n">
+      <c r="P4" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q4" s="9" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="R4" s="9" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="S4" s="9" t="n">
         <v>19.7</v>
       </c>
-      <c r="R4" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="V4" s="11" t="n">
+      <c r="T4" s="9" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="U4" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V4" s="9" t="n">
         <v>17.8</v>
       </c>
       <c r="W4" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="X4" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v>9.5</v>
+      <c r="X4" s="9" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Y4" s="9" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="Z4" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -880,7 +883,7 @@
       <c r="G5" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="H5" s="11" t="n">
+      <c r="H5" s="3" t="n">
         <v>13.5</v>
       </c>
       <c r="I5" s="3" t="n">
@@ -895,26 +898,26 @@
       <c r="L5" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="N5" s="3" t="n">
+      <c r="N5" s="9" t="n">
         <v>15.8</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>98.8</v>
+        <v>98</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q5" s="9" t="n">
         <v>21.3</v>
       </c>
       <c r="R5" s="9" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="S5" s="9" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="T5" s="9" t="n">
         <v>81</v>
@@ -922,20 +925,20 @@
       <c r="U5" s="9" t="n">
         <v>4.8</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="V5" s="9" t="n">
         <v>20.3</v>
       </c>
       <c r="W5" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="X5" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="Y5" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="Z5" s="3" t="n">
-        <v>6.6</v>
+      <c r="X5" s="9" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="Y5" s="9" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="Z5" s="9" t="n">
+        <v>3.9</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -962,10 +965,10 @@
       <c r="F6" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="G6" s="11" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="H6" s="11" t="n">
+      <c r="G6" s="9" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="I6" s="3" t="n">
@@ -975,50 +978,52 @@
         <v>1.7</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="9" t="n">
         <v>14.3</v>
       </c>
-      <c r="M6" s="13" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="N6" s="3" t="n">
+      <c r="M6" s="9" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="N6" s="9" t="n">
         <v>16.1</v>
       </c>
-      <c r="O6" s="3" t="n">
+      <c r="O6" s="9" t="n">
         <v>99</v>
       </c>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="n">
+      <c r="P6" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q6" s="9" t="n">
         <v>22.2</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="S6" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="V6" s="3" t="n">
+      <c r="S6" s="9" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="T6" s="9" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="U6" s="9" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="V6" s="9" t="n">
         <v>18.8</v>
       </c>
       <c r="W6" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="X6" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="Z6" s="3" t="n">
-        <v>93</v>
+      <c r="X6" s="9" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="Y6" s="9" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="Z6" s="9" t="n">
+        <v>1.1</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1063,47 +1068,47 @@
       <c r="L7" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="9" t="n">
         <v>15.2</v>
       </c>
-      <c r="N7" s="3" t="n">
+      <c r="N7" s="9" t="n">
         <v>17.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Q7" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q7" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="R7" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="T7" s="3" t="n">
-        <v>77</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V7" s="11" t="n">
+      <c r="R7" s="9" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="S7" s="9" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="T7" s="9" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="U7" s="9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V7" s="9" t="n">
         <v>18.8</v>
       </c>
       <c r="W7" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Z7" s="3" t="n">
-        <v>33.5</v>
+        <v>16.1</v>
+      </c>
+      <c r="X7" s="9" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="Y7" s="9" t="n">
+        <v>84</v>
+      </c>
+      <c r="Z7" s="9" t="n">
+        <v>3.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1130,8 +1135,8 @@
       <c r="F8" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="G8" s="3" t="n">
-        <v>90.59999999999999</v>
+      <c r="G8" s="9" t="n">
+        <v>9.6</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>14.2</v>
@@ -1140,55 +1145,55 @@
         <v>0.8</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>11.7</v>
+        <v>1.1</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="9" t="n">
         <v>15.2</v>
       </c>
-      <c r="M8" s="11" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="N8" s="3" t="n">
+      <c r="M8" s="9" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="N8" s="9" t="n">
         <v>17.1</v>
       </c>
-      <c r="O8" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="S8" s="3" t="n">
+      <c r="O8" s="9" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="P8" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q8" s="9" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="R8" s="9" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="S8" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="T8" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="U8" s="3" t="n">
+      <c r="T8" s="9" t="n">
+        <v>73</v>
+      </c>
+      <c r="U8" s="9" t="n">
         <v>7.2</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" s="9" t="n">
         <v>19.8</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>17.8</v>
       </c>
-      <c r="X8" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="Y8" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="Z8" s="3" t="n">
-        <v>4</v>
+      <c r="X8" s="9" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="Y8" s="9" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="Z8" s="9" t="n">
+        <v>2.7</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1204,7 +1209,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>182.5</v>
+        <v>1825.2</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>126.5</v>
@@ -1225,52 +1230,52 @@
         <v>6.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="K9" s="12" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="K9" s="10" t="n">
         <v>28.9</v>
       </c>
-      <c r="L9" s="12" t="n">
+      <c r="L9" s="10" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="M9" s="12" t="n">
+      <c r="M9" s="9" t="n">
         <v>74.3</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>95.3</v>
+        <v>93</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q9" s="12" t="n">
+      <c r="Q9" s="9" t="n">
         <v>103.3</v>
       </c>
-      <c r="R9" s="12" t="n">
+      <c r="R9" s="10" t="n">
         <v>89.90000000000001</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>198.6</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>891.8</v>
+        <v>895.5</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="V9" s="12" t="n">
-        <v>95.3</v>
-      </c>
-      <c r="W9" s="9" t="n">
+      <c r="V9" s="9" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="W9" s="10" t="n">
         <v>87.2</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>94.8</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>9429</v>
+        <v>29</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>16.1</v>
@@ -1310,55 +1315,55 @@
         <v>1.3</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L10" s="12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>1100.1</v>
+      </c>
+      <c r="L10" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="M10" s="12" t="n">
+      <c r="M10" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="N10" s="3" t="n">
+      <c r="N10" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="O10" s="3" t="n">
+      <c r="O10" s="9" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="P10" s="3" t="n">
+      <c r="P10" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q10" s="12" t="n">
+      <c r="Q10" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="R10" s="12" t="n">
+      <c r="R10" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="S10" s="3" t="n">
+      <c r="S10" s="9" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="T10" s="9" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="U10" s="9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V10" s="9" t="n">
         <v>19.1</v>
-      </c>
-      <c r="T10" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="U10" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="V10" s="12" t="n">
-        <v>191.4</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="X10" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>3.2</v>
+      <c r="X10" s="9" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="Y10" s="9" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="Z10" s="9" t="n">
+        <v>2.2</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1380,10 +1385,10 @@
         <v>23.4</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>16.1</v>
+        <v>7.2</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>18.7</v>
+        <v>15.3</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>10.1</v>
@@ -1397,17 +1402,17 @@
       <c r="J11" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="K11" s="11" t="n">
+      <c r="K11" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="L11" s="9" t="n">
-        <v>12.28</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N11" s="11" t="n">
-        <v>13.6</v>
+      <c r="L11" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="M11" s="9" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="N11" s="9" t="n">
+        <v>15.6</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>99</v>
@@ -1415,35 +1420,35 @@
       <c r="P11" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="13" t="n">
-        <v>2.3</v>
+      <c r="Q11" s="9" t="n">
+        <v>22.3</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>29.5</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>1220.4</v>
+        <v>72</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="V11" s="13" t="n">
-        <v>15.86</v>
+        <v>7.4</v>
+      </c>
+      <c r="V11" s="9" t="n">
+        <v>18.6</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="X11" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="Z11" s="3" t="n">
-        <v>10.9</v>
+      <c r="X11" s="9" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="Y11" s="9" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="Z11" s="9" t="n">
+        <v>0.7</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1459,7 +1464,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>511.1</v>
+        <v>11.1</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>25.7</v>
@@ -1477,30 +1482,30 @@
         <v>10</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="M12" s="11" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="O12" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P12" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Q12" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="M12" s="9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="N12" s="9" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="O12" s="9" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="P12" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q12" s="9" t="n">
         <v>24.3</v>
       </c>
       <c r="R12" s="3" t="n">
@@ -1515,20 +1520,20 @@
       <c r="U12" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="V12" s="3" t="n">
+      <c r="V12" s="9" t="n">
         <v>21.2</v>
       </c>
       <c r="W12" s="9" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="X12" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="X12" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="Y12" s="3" t="n">
-        <v>281</v>
-      </c>
-      <c r="Z12" s="3" t="n">
-        <v>2.8</v>
+      <c r="Y12" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="Z12" s="9" t="n">
+        <v>3.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1562,7 +1567,7 @@
         <v>8.6</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.8</v>
@@ -1570,50 +1575,50 @@
       <c r="K13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="9" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="M13" s="3" t="n">
+      <c r="L13" s="3" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="M13" s="9" t="n">
         <v>11.6</v>
       </c>
-      <c r="N13" s="3" t="n">
-        <v>12.5</v>
+      <c r="N13" s="9" t="n">
+        <v>13.5</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="Q13" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q13" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="R13" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="S13" s="3" t="n">
+      <c r="R13" s="9" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="S13" s="9" t="n">
         <v>19.7</v>
       </c>
-      <c r="T13" s="3" t="n">
-        <v>1866.8</v>
-      </c>
-      <c r="U13" s="3" t="n">
+      <c r="T13" s="9" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="U13" s="9" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V13" s="3" t="n">
+      <c r="V13" s="9" t="n">
         <v>20.8</v>
       </c>
       <c r="W13" s="9" t="n">
         <v>17.8</v>
       </c>
-      <c r="X13" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="Y13" s="3" t="n">
-        <v>726</v>
-      </c>
-      <c r="Z13" s="3" t="n">
-        <v>6</v>
+      <c r="X13" s="9" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="Y13" s="9" t="n">
+        <v>83</v>
+      </c>
+      <c r="Z13" s="9" t="n">
+        <v>4.2</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1629,7 +1634,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>331.9</v>
+        <v>531.1</v>
       </c>
       <c r="D14" s="9" t="n">
         <v>26.8</v>
@@ -1647,7 +1652,7 @@
         <v>8.9</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>3.6</v>
@@ -1655,22 +1660,22 @@
       <c r="K14" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="L14" s="9" t="n">
+      <c r="L14" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="M14" s="3" t="n">
+      <c r="M14" s="9" t="n">
         <v>12.7</v>
       </c>
-      <c r="N14" s="3" t="n">
-        <v>14.5</v>
+      <c r="N14" s="9" t="n">
+        <v>14.8</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q14" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q14" s="9" t="n">
         <v>22.6</v>
       </c>
       <c r="R14" s="3" t="n">
@@ -1685,20 +1690,20 @@
       <c r="U14" s="3" t="n">
         <v>7.8</v>
       </c>
-      <c r="V14" s="3" t="n">
+      <c r="V14" s="9" t="n">
         <v>20.6</v>
       </c>
       <c r="W14" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="X14" s="3" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="Y14" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Z14" s="3" t="n">
-        <v>4</v>
+      <c r="X14" s="9" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Y14" s="9" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="Z14" s="9" t="n">
+        <v>3.1</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1723,7 +1728,7 @@
         <v>14.1</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>20.8</v>
+        <v>20.4</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>22.6</v>
@@ -1732,25 +1737,25 @@
         <v>10.7</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>10.9</v>
+        <v>2.4</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>13.2</v>
+        <v>3.2</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L15" s="9" t="n">
+      <c r="L15" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="M15" s="11" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v>1.5</v>
+      <c r="M15" s="9" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="N15" s="9" t="n">
+        <v>15.9</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>97</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0.6</v>
@@ -1770,20 +1775,20 @@
       <c r="U15" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="V15" s="9" t="n">
         <v>19.2</v>
       </c>
       <c r="W15" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="X15" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="Y15" s="3" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="Z15" s="3" t="n">
-        <v>3.6</v>
+      <c r="X15" s="9" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="Y15" s="9" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="Z15" s="9" t="n">
+        <v>2.5</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1799,19 +1804,19 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2306.9</v>
+        <v>230.6</v>
       </c>
       <c r="D16" s="9" t="n">
         <v>127.2</v>
       </c>
-      <c r="E16" s="9" t="n">
-        <v>68</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>97</v>
-      </c>
-      <c r="G16" s="13" t="n">
-        <v>16.2</v>
+      <c r="E16" s="10" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>62</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>48.9</v>
@@ -1820,53 +1825,53 @@
         <v>9.699999999999999</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="K16" s="12" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="K16" s="10" t="n">
         <v>19.6</v>
       </c>
-      <c r="L16" s="9" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="M16" s="12" t="n">
-        <v>66.2</v>
+      <c r="L16" s="10" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="M16" s="9" t="n">
+        <v>66.5</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>45.6</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>432</v>
+        <v>95</v>
       </c>
       <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="12" t="n">
-        <v>115.7</v>
-      </c>
-      <c r="R16" s="12" t="n">
-        <v>92.90000000000001</v>
+      <c r="Q16" s="9" t="n">
+        <v>118.7</v>
+      </c>
+      <c r="R16" s="10" t="n">
+        <v>92.40000000000001</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>91.59999999999999</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>313</v>
+        <v>13</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>255.8</v>
-      </c>
-      <c r="V16" s="12" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="V16" s="9" t="n">
         <v>100.4</v>
       </c>
-      <c r="W16" s="9" t="n">
+      <c r="W16" s="10" t="n">
         <v>90.90000000000001</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>99.2</v>
+        <v>99.8</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>921</v>
+        <v>24</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>118.4</v>
+        <v>18.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1882,19 +1887,19 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>461.4</v>
+        <v>51.4</v>
       </c>
       <c r="D17" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="E17" s="9" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="G17" s="13" t="n">
-        <v>11.2</v>
+      <c r="E17" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>12.4</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1905,13 +1910,13 @@
       <c r="J17" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="K17" s="11" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="L17" s="9" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="M17" s="12" t="n">
+      <c r="K17" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="L17" s="10" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="M17" s="9" t="n">
         <v>13.2</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1923,10 +1928,10 @@
       <c r="P17" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q17" s="12" t="n">
+      <c r="Q17" s="9" t="n">
         <v>23.7</v>
       </c>
-      <c r="R17" s="12" t="n">
+      <c r="R17" s="10" t="n">
         <v>18.5</v>
       </c>
       <c r="S17" s="3" t="n">
@@ -1935,23 +1940,23 @@
       <c r="T17" s="3" t="n">
         <v>62.6</v>
       </c>
-      <c r="U17" s="11" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="V17" s="12" t="n">
-        <v>1.4</v>
+      <c r="U17" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="V17" s="9" t="n">
+        <v>20.1</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>18.2</v>
       </c>
-      <c r="X17" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="Y17" s="3" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="Z17" s="3" t="n">
-        <v>3.7</v>
+      <c r="X17" s="9" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="Y17" s="9" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="Z17" s="9" t="n">
+        <v>2.6</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1993,35 +1998,35 @@
       <c r="K18" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L18" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="M18" s="3" t="n">
+      <c r="L18" s="9" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="M18" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="N18" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O18" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q18" s="11" t="n">
-        <v>10.4</v>
+      <c r="N18" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="O18" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P18" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q18" s="9" t="n">
+        <v>22.4</v>
       </c>
       <c r="R18" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="S18" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S18" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="T18" s="3" t="n">
-        <v>174</v>
-      </c>
-      <c r="U18" s="3" t="n">
-        <v>1</v>
+      <c r="T18" s="9" t="n">
+        <v>74</v>
+      </c>
+      <c r="U18" s="9" t="n">
+        <v>7</v>
       </c>
       <c r="V18" s="9" t="n">
         <v>20.2</v>
@@ -2052,61 +2057,61 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>435.6</v>
+        <v>235.6</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="E19" s="9" t="n">
         <v>13</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>12.7</v>
       </c>
-      <c r="H19" s="11" t="n">
+      <c r="H19" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>5.7</v>
+        <v>3.1</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>4.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L19" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L19" s="9" t="n">
         <v>14.2</v>
       </c>
-      <c r="M19" s="11" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>47</v>
-      </c>
-      <c r="P19" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q19" s="3" t="n">
-        <v>24.3</v>
+      <c r="M19" s="9" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="N19" s="9" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="O19" s="9" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="P19" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q19" s="9" t="n">
+        <v>24.5</v>
       </c>
       <c r="R19" s="9" t="n">
         <v>18.2</v>
       </c>
-      <c r="S19" s="11" t="n">
-        <v>79.40000000000001</v>
-      </c>
-      <c r="T19" s="3" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>13.4</v>
+      <c r="S19" s="9" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="T19" s="9" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="U19" s="9" t="n">
+        <v>9.9</v>
       </c>
       <c r="V19" s="9" t="n">
         <v>19.4</v>
@@ -2137,13 +2142,13 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1417.9</v>
+        <v>17.9</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>12.54</v>
+        <v>12.4</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>19.8</v>
@@ -2163,49 +2168,49 @@
       <c r="K20" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" s="9" t="n">
         <v>12.6</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="N20" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>184.4</v>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q20" s="3" t="n">
-        <v>13.4</v>
+      <c r="N20" s="9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="O20" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P20" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q20" s="9" t="n">
+        <v>23.4</v>
       </c>
       <c r="R20" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="S20" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="T20" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="U20" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="V20" s="3" t="n">
-        <v>12.2</v>
+      <c r="S20" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" s="9" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="U20" s="9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="V20" s="9" t="n">
+        <v>19.2</v>
       </c>
       <c r="W20" s="9" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X20" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="X20" s="9" t="n">
         <v>19.4</v>
       </c>
-      <c r="Y20" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="Z20" s="3" t="n">
+      <c r="Y20" s="9" t="n">
+        <v>87</v>
+      </c>
+      <c r="Z20" s="9" t="n">
         <v>2.9</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -2222,13 +2227,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>379.3</v>
+        <v>371.3</v>
       </c>
       <c r="D21" s="9" t="n">
         <v>25.6</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>19.8</v>
@@ -2243,42 +2248,42 @@
         <v>1.3</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K21" s="11" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="L21" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="L21" s="9" t="n">
         <v>16.5</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="9" t="n">
         <v>16.5</v>
       </c>
-      <c r="N21" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="O21" s="3" t="n">
+      <c r="N21" s="9" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="O21" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="P21" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q21" s="3" t="n">
+      <c r="P21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="9" t="n">
         <v>20.7</v>
       </c>
       <c r="R21" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="S21" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="T21" s="3" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="U21" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="V21" s="3" t="n">
+      <c r="S21" s="9" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="T21" s="9" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="U21" s="9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V21" s="9" t="n">
         <v>16.6</v>
       </c>
       <c r="W21" s="9" t="n">
@@ -2287,11 +2292,11 @@
       <c r="X21" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="Y21" s="3" t="n">
-        <v>918.1</v>
-      </c>
-      <c r="Z21" s="3" t="n">
-        <v>8.4</v>
+      <c r="Y21" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="Z21" s="9" t="n">
+        <v>0.2</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2313,7 +2318,7 @@
         <v>25.8</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>19.5</v>
@@ -2331,52 +2336,52 @@
         <v>3.5</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="L22" s="13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M22" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L22" s="9" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="M22" s="9" t="n">
         <v>12.9</v>
       </c>
-      <c r="N22" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="O22" s="3" t="n">
-        <v>297</v>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q22" s="3" t="n">
+      <c r="N22" s="9" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="O22" s="9" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="P22" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q22" s="9" t="n">
         <v>24.6</v>
       </c>
       <c r="R22" s="9" t="n">
         <v>18.7</v>
       </c>
-      <c r="S22" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="T22" s="3" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="U22" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="V22" s="3" t="n">
+      <c r="S22" s="9" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="T22" s="9" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="U22" s="9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="V22" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="W22" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="X22" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="Y22" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="Z22" s="3" t="n">
-        <v>1.8</v>
+      <c r="X22" s="9" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="Y22" s="9" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="Z22" s="9" t="n">
+        <v>1.2</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2392,12 +2397,12 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2089.4</v>
+        <v>208.9</v>
       </c>
       <c r="D23" s="9" t="n">
         <v>128.2</v>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="E23" s="9" t="n">
         <v>66.8</v>
       </c>
       <c r="F23" s="9" t="n">
@@ -2415,14 +2420,14 @@
       <c r="J23" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="K23" s="12" t="n">
+      <c r="K23" s="10" t="n">
         <v>27.4</v>
       </c>
-      <c r="L23" s="12" t="n">
-        <v>80.7</v>
-      </c>
-      <c r="M23" s="12" t="n">
-        <v>69.59999999999999</v>
+      <c r="L23" s="9" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="M23" s="9" t="n">
+        <v>68.59999999999999</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>7.9</v>
@@ -2431,35 +2436,35 @@
         <v>489</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="Q23" s="12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q23" s="9" t="n">
         <v>115.6</v>
       </c>
-      <c r="R23" s="9" t="n">
+      <c r="R23" s="10" t="n">
         <v>91.5</v>
       </c>
       <c r="S23" s="3" t="inlineStr"/>
       <c r="T23" s="3" t="n">
-        <v>232.8</v>
+        <v>328</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>149.8</v>
-      </c>
-      <c r="V23" s="12" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="V23" s="9" t="n">
         <v>94.3</v>
       </c>
-      <c r="W23" s="12" t="n">
+      <c r="W23" s="10" t="n">
         <v>86.3</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>93</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>429.8</v>
+        <v>29</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>116.3</v>
+        <v>16.3</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2475,7 +2480,7 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>417.9</v>
+        <v>17.9</v>
       </c>
       <c r="D24" s="9" t="n">
         <v>25.6</v>
@@ -2486,23 +2491,25 @@
       <c r="F24" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="G24" s="11" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="H24" s="11" t="n">
+      <c r="G24" s="9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="H24" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="12" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="M24" s="12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L24" s="9" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="M24" s="9" t="n">
         <v>13.9</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2514,35 +2521,35 @@
       <c r="P24" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q24" s="12" t="n">
+      <c r="Q24" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="R24" s="9" t="n">
+      <c r="R24" s="10" t="n">
         <v>18.3</v>
       </c>
-      <c r="S24" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="T24" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="U24" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="V24" s="12" t="n">
+      <c r="S24" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="T24" s="9" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="U24" s="9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="V24" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="W24" s="12" t="n">
+      <c r="W24" s="10" t="n">
         <v>17.3</v>
       </c>
-      <c r="X24" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="Y24" s="3" t="n">
-        <v>85.8</v>
-      </c>
-      <c r="Z24" s="3" t="n">
-        <v>8.800000000000001</v>
+      <c r="X24" s="9" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="Y24" s="9" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="Z24" s="9" t="n">
+        <v>2.1</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2558,7 +2565,7 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>233.6</v>
+        <v>233.5</v>
       </c>
       <c r="D25" s="9" t="n">
         <v>23.1</v>
@@ -2572,7 +2579,7 @@
       <c r="G25" s="9" t="n">
         <v>7.6</v>
       </c>
-      <c r="H25" s="11" t="n">
+      <c r="H25" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="I25" s="3" t="n">
@@ -2582,7 +2589,7 @@
         <v>0.8</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="L25" s="9" t="n">
         <v>16.9</v>
@@ -2600,34 +2607,34 @@
         <v>0.4</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="R25" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="R25" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="S25" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="T25" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="U25" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V25" s="11" t="n">
-        <v>27.9</v>
+      <c r="S25" s="9" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="T25" s="9" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="U25" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V25" s="9" t="n">
+        <v>17</v>
       </c>
       <c r="W25" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="X25" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y25" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="Z25" s="3" t="n">
-        <v>1</v>
+      <c r="X25" s="9" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Y25" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z25" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2643,7 +2650,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>228.3</v>
+        <v>268.3</v>
       </c>
       <c r="D26" s="9" t="n">
         <v>22.4</v>
@@ -2658,7 +2665,7 @@
         <v>7.1</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>13.5</v>
+        <v>13.2</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>0.7</v>
@@ -2669,47 +2676,51 @@
       <c r="K26" s="3" t="n">
         <v>17.7</v>
       </c>
-      <c r="L26" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="M26" s="11" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="O26" s="3" t="n">
-        <v>108</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>81</v>
+      <c r="L26" s="15" t="n">
+        <v>-15.8</v>
+      </c>
+      <c r="M26" s="15" t="n">
+        <v>-15.8</v>
+      </c>
+      <c r="N26" s="9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O26" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="P26" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Q26" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="R26" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="S26" s="11" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="T26" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="U26" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V26" s="3" t="n">
+      <c r="R26" s="9" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="S26" s="9" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="T26" s="9" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="U26" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" s="9" t="n">
         <v>15.6</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>15.3</v>
       </c>
-      <c r="X26" s="3" t="inlineStr"/>
-      <c r="Y26" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="Z26" s="3" t="inlineStr"/>
+      <c r="X26" s="9" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="Y26" s="9" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="Z26" s="9" t="n">
+        <v>0.3</v>
+      </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -2724,7 +2735,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>435.6</v>
+        <v>35.6</v>
       </c>
       <c r="D27" s="9" t="n">
         <v>24.5</v>
@@ -2735,14 +2746,14 @@
       <c r="F27" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="G27" s="11" t="n">
-        <v>12.2</v>
+      <c r="G27" s="9" t="n">
+        <v>11.2</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>11.7</v>
+        <v>1.1</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>1.6</v>
@@ -2750,50 +2761,50 @@
       <c r="K27" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="L27" s="13" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="M27" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="O27" s="3" t="n">
+      <c r="L27" s="9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="M27" s="9" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="N27" s="9" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="O27" s="9" t="n">
         <v>99</v>
       </c>
-      <c r="P27" s="3" t="n">
+      <c r="P27" s="9" t="n">
         <v>0.2</v>
       </c>
       <c r="Q27" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="R27" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="S27" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="T27" s="3" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="U27" s="3" t="n">
+      <c r="R27" s="9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S27" s="9" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="T27" s="9" t="n">
+        <v>87</v>
+      </c>
+      <c r="U27" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="V27" s="11" t="n">
+      <c r="V27" s="9" t="n">
         <v>19</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="X27" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Y27" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="Z27" s="3" t="n">
-        <v>2.8</v>
+      <c r="X27" s="9" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="Y27" s="9" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="Z27" s="9" t="n">
+        <v>1.8</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2830,7 +2841,7 @@
         <v>0.7</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>32.8</v>
@@ -2838,14 +2849,14 @@
       <c r="L28" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="M28" s="3" t="n">
+      <c r="M28" s="9" t="n">
         <v>14.3</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>16.2</v>
+        <v>12.2</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>98.59999999999999</v>
+        <v>98</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>0.4</v>
@@ -2853,17 +2864,17 @@
       <c r="Q28" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="R28" s="11" t="n">
+      <c r="R28" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="S28" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="T28" s="3" t="n">
-        <v>48.1</v>
-      </c>
-      <c r="U28" s="3" t="n">
-        <v>9</v>
+      <c r="S28" s="9" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="T28" s="9" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="U28" s="9" t="n">
+        <v>3.4</v>
       </c>
       <c r="V28" s="9" t="n">
         <v>17.2</v>
@@ -2894,21 +2905,21 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>309.7</v>
+        <v>309.1</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>23.7</v>
+        <v>23.1</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>13.3</v>
+        <v>14</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="G29" s="3" t="n">
+      <c r="G29" s="9" t="n">
         <v>9.1</v>
       </c>
-      <c r="H29" s="11" t="n">
+      <c r="H29" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="I29" s="3" t="n">
@@ -2918,19 +2929,19 @@
         <v>1.3</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L29" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="L29" s="3" t="n">
         <v>13.7</v>
       </c>
-      <c r="M29" s="11" t="n">
+      <c r="M29" s="9" t="n">
         <v>15</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>74.40000000000001</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>0.2</v>
@@ -2938,32 +2949,32 @@
       <c r="Q29" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="R29" s="11" t="n">
+      <c r="R29" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="S29" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="T29" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="U29" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="V29" s="11" t="n">
-        <v>35.8</v>
+      <c r="S29" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="T29" s="9" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="U29" s="9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="V29" s="9" t="n">
+        <v>15.8</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>15.5</v>
       </c>
       <c r="X29" s="9" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="Y29" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="Z29" s="3" t="n">
-        <v>0.6</v>
+        <v>17.6</v>
+      </c>
+      <c r="Y29" s="9" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="Z29" s="9" t="n">
+        <v>0.3</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2979,12 +2990,12 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="D30" s="12" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="D30" s="9" t="n">
         <v>116.8</v>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="E30" s="9" t="n">
         <v>71.90000000000001</v>
       </c>
       <c r="F30" s="9" t="n">
@@ -3002,39 +3013,39 @@
       <c r="J30" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="K30" s="12" t="n">
+      <c r="K30" s="10" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="L30" s="12" t="n">
+      <c r="L30" s="10" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="M30" s="12" t="n">
+      <c r="M30" s="10" t="n">
         <v>74.3</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>494.8</v>
       </c>
       <c r="P30" s="3" t="inlineStr"/>
       <c r="Q30" s="9" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="R30" s="12" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="R30" s="10" t="n">
         <v>89.2</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>413.1</v>
+        <v>13.1</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="V30" s="12" t="n">
-        <v>8.5</v>
+      <c r="V30" s="9" t="n">
+        <v>84.59999999999999</v>
       </c>
       <c r="W30" s="9" t="n">
         <v>82.40000000000001</v>
@@ -3043,10 +3054,10 @@
         <v>92.09999999999999</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>9428</v>
+        <v>475</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>9.4</v>
+        <v>5.4</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3073,8 +3084,8 @@
       <c r="F31" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="G31" s="3" t="n">
-        <v>90.40000000000001</v>
+      <c r="G31" s="9" t="n">
+        <v>9</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>12.5</v>
@@ -3086,50 +3097,50 @@
         <v>0.9</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="12" t="n">
+      <c r="L31" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="M31" s="12" t="n">
+      <c r="M31" s="10" t="n">
         <v>14.9</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>60.4</v>
+        <v>22.8</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0.1</v>
+        <v>20.1</v>
       </c>
       <c r="Q31" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="R31" s="12" t="n">
-        <v>87.8</v>
-      </c>
-      <c r="S31" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="T31" s="3" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="U31" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="V31" s="12" t="n">
+      <c r="R31" s="10" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="S31" s="9" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="T31" s="9" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="U31" s="9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V31" s="9" t="n">
         <v>17</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>16.3</v>
       </c>
       <c r="X31" s="9" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="Y31" s="9" t="n">
-        <v>95</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="Z31" s="9" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3145,58 +3156,62 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>364.2</v>
-      </c>
-      <c r="D32" s="13" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="E32" s="11" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F32" s="13" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="G32" s="3" t="n">
+        <v>364.6</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G32" s="9" t="n">
         <v>14.3</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="L32" s="13" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="M32" s="13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="O32" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q32" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K32" s="9" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="L32" s="9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="M32" s="9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="N32" s="9" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="O32" s="9" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="P32" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q32" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="R32" s="11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="S32" s="3" t="inlineStr"/>
-      <c r="T32" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="U32" s="3" t="inlineStr"/>
+      <c r="R32" s="9" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="S32" s="9" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="T32" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="U32" s="9" t="n">
+        <v>0.2</v>
+      </c>
       <c r="V32" s="9" t="n">
         <v>16.6</v>
       </c>
@@ -3226,7 +3241,7 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>411.2</v>
+        <v>11.2</v>
       </c>
       <c r="D33" s="9" t="n">
         <v>23.7</v>
@@ -3240,7 +3255,7 @@
       <c r="G33" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="H33" s="11" t="n">
+      <c r="H33" s="3" t="n">
         <v>11.5</v>
       </c>
       <c r="I33" s="3" t="n">
@@ -3249,38 +3264,38 @@
       <c r="J33" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="K33" s="9" t="n">
         <v>7.2</v>
       </c>
-      <c r="L33" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="M33" s="3" t="n">
+      <c r="L33" s="9" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="M33" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="N33" s="11" t="n">
-        <v>9161.9</v>
-      </c>
-      <c r="O33" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P33" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q33" s="3" t="n">
+      <c r="N33" s="9" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="O33" s="9" t="n">
+        <v>120.4</v>
+      </c>
+      <c r="P33" s="9" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="Q33" s="9" t="n">
         <v>21.2</v>
       </c>
-      <c r="R33" s="3" t="n">
+      <c r="R33" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="S33" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="T33" s="3" t="n">
-        <v>71.8</v>
-      </c>
-      <c r="U33" s="3" t="n">
-        <v>8.6</v>
+      <c r="S33" s="9" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="T33" s="9" t="n">
+        <v>84</v>
+      </c>
+      <c r="U33" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="V33" s="9" t="n">
         <v>17.8</v>
@@ -3313,17 +3328,17 @@
       <c r="C34" s="3" t="n">
         <v>211.4</v>
       </c>
-      <c r="D34" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="E34" s="3" t="n">
+      <c r="D34" s="9" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E34" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="F34" s="3" t="n">
+      <c r="F34" s="9" t="n">
         <v>17.4</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>14.6</v>
+        <v>4.6</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>14.2</v>
@@ -3334,41 +3349,41 @@
       <c r="J34" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="K34" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="L34" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="N34" s="3" t="n">
+      <c r="K34" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L34" s="9" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="M34" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="N34" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="O34" s="3" t="n">
+      <c r="O34" s="9" t="n">
         <v>99</v>
       </c>
-      <c r="P34" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q34" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="R34" s="3" t="n">
+      <c r="P34" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q34" s="9" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="R34" s="9" t="n">
         <v>15.8</v>
       </c>
-      <c r="S34" s="3" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="T34" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="U34" s="3" t="n">
-        <v>2.8</v>
+      <c r="S34" s="9" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="T34" s="9" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="U34" s="9" t="n">
+        <v>1.3</v>
       </c>
       <c r="V34" s="9" t="n">
-        <v>16.9</v>
+        <v>16.4</v>
       </c>
       <c r="W34" s="9" t="n">
         <v>15.2</v>
@@ -3377,10 +3392,10 @@
         <v>17.3</v>
       </c>
       <c r="Y34" s="9" t="n">
-        <v>89.7</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="Z34" s="9" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3396,13 +3411,13 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>477.8</v>
+        <v>77.8</v>
       </c>
       <c r="D35" s="9" t="n">
         <v>24.1</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="F35" s="9" t="n">
         <v>18.1</v>
@@ -3419,53 +3434,53 @@
       <c r="J35" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="M35" s="11" t="n">
+      <c r="M35" s="9" t="n">
         <v>12.3</v>
       </c>
-      <c r="N35" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="O35" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P35" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q35" s="11" t="n">
+      <c r="N35" s="9" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="O35" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P35" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q35" s="9" t="n">
         <v>23.9</v>
       </c>
-      <c r="R35" s="3" t="n">
+      <c r="R35" s="9" t="n">
         <v>18.3</v>
       </c>
-      <c r="S35" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="T35" s="3" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="U35" s="3" t="n">
-        <v>11.8</v>
+      <c r="S35" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="T35" s="9" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="U35" s="9" t="n">
+        <v>8.6</v>
       </c>
       <c r="V35" s="9" t="n">
-        <v>18.9</v>
+        <v>18.4</v>
       </c>
       <c r="W35" s="9" t="n">
-        <v>16.5</v>
+        <v>15.6</v>
       </c>
       <c r="X35" s="9" t="n">
-        <v>18.8</v>
+        <v>17.7</v>
       </c>
       <c r="Y35" s="9" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="Z35" s="9" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3481,7 +3496,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>613.2</v>
+        <v>13.2</v>
       </c>
       <c r="D36" s="9" t="n">
         <v>25.2</v>
@@ -3496,7 +3511,7 @@
         <v>11.3</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>10.7</v>
+        <v>10.9</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>3.3</v>
@@ -3504,38 +3519,38 @@
       <c r="J36" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="L36" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="M36" s="3" t="n">
+      <c r="M36" s="9" t="n">
         <v>14.6</v>
       </c>
-      <c r="N36" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="O36" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="P36" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q36" s="11" t="n">
-        <v>21</v>
-      </c>
-      <c r="R36" s="3" t="n">
+      <c r="N36" s="9" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="O36" s="9" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="P36" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q36" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="R36" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="S36" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="T36" s="3" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="U36" s="3" t="n">
-        <v>12.4</v>
+      <c r="S36" s="9" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="T36" s="9" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="U36" s="9" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="V36" s="9" t="n">
         <v>20.8</v>
@@ -3566,55 +3581,55 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2078.2</v>
-      </c>
-      <c r="D37" s="12" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="D37" s="10" t="n">
         <v>118.4</v>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="E37" s="10" t="n">
         <v>66.09999999999999</v>
       </c>
-      <c r="F37" s="12" t="n">
-        <v>292.2</v>
-      </c>
-      <c r="G37" s="13" t="n">
-        <v>35.2</v>
+      <c r="F37" s="9" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="G37" s="9" t="n">
+        <v>52.3</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>56.7</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="K37" s="12" t="n">
-        <v>507.9</v>
-      </c>
-      <c r="L37" s="12" t="n">
-        <v>68.3</v>
-      </c>
-      <c r="M37" s="12" t="n">
-        <v>68.59999999999999</v>
+      <c r="K37" s="9" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="L37" s="9" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="M37" s="9" t="n">
+        <v>70.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>11.7</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="Q37" s="12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q37" s="9" t="n">
         <v>101</v>
       </c>
-      <c r="R37" s="12" t="n">
-        <v>59.9</v>
+      <c r="R37" s="9" t="n">
+        <v>84.90000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>380.9</v>
@@ -3623,16 +3638,16 @@
         <v>33.2</v>
       </c>
       <c r="V37" s="9" t="n">
-        <v>91</v>
-      </c>
-      <c r="W37" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="W37" s="10" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>88</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>429.8</v>
+        <v>429.5</v>
       </c>
       <c r="Z37" s="3" t="inlineStr"/>
       <c r="AA37" s="3" t="inlineStr">
@@ -3649,61 +3664,61 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>415.6</v>
-      </c>
-      <c r="D38" s="12" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D38" s="10" t="n">
         <v>23.6</v>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E38" s="10" t="n">
         <v>13.1</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="F38" s="9" t="n">
         <v>18.4</v>
       </c>
       <c r="G38" s="9" t="n">
         <v>10.5</v>
       </c>
-      <c r="H38" s="11" t="n">
+      <c r="H38" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="I38" s="11" t="n">
+      <c r="I38" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L38" s="9" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="M38" s="9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="N38" s="9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="O38" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P38" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q38" s="9" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="R38" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="J38" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L38" s="12" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="M38" s="12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="N38" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="O38" s="3" t="n">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="P38" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="Q38" s="12" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="R38" s="12" t="n">
-        <v>97</v>
-      </c>
-      <c r="S38" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="T38" s="3" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="U38" s="3" t="n">
-        <v>6.6</v>
+      <c r="S38" s="9" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="T38" s="9" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="U38" s="9" t="n">
+        <v>4.3</v>
       </c>
       <c r="V38" s="9" t="n">
         <v>18</v>
@@ -3734,76 +3749,76 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>624.3</v>
+        <v>24.3</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>25.1</v>
+        <v>25.9</v>
       </c>
       <c r="E39" s="9" t="n">
         <v>11.1</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G39" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G39" s="9" t="n">
         <v>14.8</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>7.6</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="K39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="9" t="n">
+      <c r="L39" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="M39" s="9" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="N39" s="9" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="O39" s="9" t="n">
-        <v>91</v>
-      </c>
-      <c r="P39" s="9" t="n">
-        <v>1.2</v>
+      <c r="M39" s="15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q39" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="R39" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="S39" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T39" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="U39" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="V39" s="13" t="n">
-        <v>71.5</v>
+      <c r="R39" s="9" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="S39" s="9" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="T39" s="9" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="U39" s="9" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="V39" s="9" t="n">
+        <v>21.5</v>
       </c>
       <c r="W39" s="9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="X39" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y39" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="Z39" s="3" t="n">
-        <v>62.8</v>
+        <v>16.8</v>
+      </c>
+      <c r="X39" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="Y39" s="9" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="Z39" s="9" t="n">
+        <v>6.5</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3819,30 +3834,30 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>637.7</v>
+        <v>37.7</v>
       </c>
       <c r="D40" s="9" t="n">
         <v>26</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="G40" s="11" t="n">
-        <v>65.3</v>
+      <c r="G40" s="9" t="n">
+        <v>16.3</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>15.3</v>
+        <v>5.3</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>3.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K40" s="3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K40" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
@@ -3858,37 +3873,37 @@
         <v>98</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q40" s="9" t="n">
         <v>25.4</v>
       </c>
-      <c r="R40" s="3" t="n">
+      <c r="R40" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="S40" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="T40" s="3" t="n">
-        <v>1948.8</v>
-      </c>
-      <c r="U40" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="V40" s="3" t="n">
+      <c r="S40" s="9" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="T40" s="9" t="n">
+        <v>62</v>
+      </c>
+      <c r="U40" s="9" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="V40" s="9" t="n">
         <v>22.3</v>
       </c>
       <c r="W40" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="X40" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="Y40" s="3" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="Z40" s="3" t="n">
-        <v>16.8</v>
+      <c r="X40" s="9" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="Y40" s="9" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="Z40" s="9" t="n">
+        <v>7.2</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3921,22 +3936,22 @@
       <c r="H41" s="3" t="inlineStr"/>
       <c r="I41" s="3" t="inlineStr"/>
       <c r="J41" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="K41" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K41" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="M41" s="13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N41" s="11" t="n">
-        <v>18.8</v>
+        <v>10.7</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>12.5</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>0.4</v>
@@ -3944,32 +3959,32 @@
       <c r="Q41" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="R41" s="3" t="n">
+      <c r="R41" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="S41" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="T41" s="3" t="n">
-        <v>947</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="V41" s="3" t="n">
+      <c r="S41" s="9" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="T41" s="9" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="U41" s="9" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="V41" s="9" t="n">
         <v>21.7</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>16.2</v>
       </c>
-      <c r="X41" s="11" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="Y41" s="3" t="n">
-        <v>239</v>
-      </c>
-      <c r="Z41" s="3" t="n">
-        <v>16.8</v>
+      <c r="X41" s="9" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="Y41" s="9" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="Z41" s="9" t="n">
+        <v>7.5</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3987,74 +4002,74 @@
       <c r="C42" s="3" t="n">
         <v>608.8</v>
       </c>
-      <c r="D42" s="13" t="n">
+      <c r="D42" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="E42" s="13" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="F42" s="13" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="G42" s="3" t="n">
+      <c r="E42" s="9" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F42" s="9" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G42" s="9" t="n">
         <v>16.5</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>5.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K42" s="3" t="n">
-        <v>10</v>
+        <v>5.9</v>
+      </c>
+      <c r="K42" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="M42" s="11" t="n">
+      <c r="M42" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="N42" s="11" t="n">
+      <c r="N42" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>18.2</v>
+        <v>98</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>26.7</v>
+        <v>26.1</v>
       </c>
       <c r="R42" s="9" t="n">
         <v>18.2</v>
       </c>
       <c r="S42" s="9" t="n">
-        <v>20.6</v>
+        <v>20.9</v>
       </c>
       <c r="T42" s="9" t="n">
-        <v>58.9</v>
+        <v>61.8</v>
       </c>
       <c r="U42" s="9" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="V42" s="3" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="V42" s="9" t="n">
         <v>22</v>
       </c>
       <c r="W42" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="X42" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="Y42" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="Z42" s="3" t="n">
-        <v>10.2</v>
+      <c r="X42" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="Y42" s="9" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="Z42" s="9" t="n">
+        <v>7.3</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4073,13 +4088,13 @@
         <v>604.4</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="G43" s="9" t="n">
         <v>13.7</v>
@@ -4091,22 +4106,22 @@
         <v>3.5</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>8</v>
+        <v>5.4</v>
+      </c>
+      <c r="K43" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="M43" s="11" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="N43" s="11" t="n">
-        <v>19.8</v>
+        <v>11.4</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="P43" s="3" t="n">
         <v>0.6</v>
@@ -4114,32 +4129,32 @@
       <c r="Q43" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="R43" s="3" t="n">
+      <c r="R43" s="9" t="n">
         <v>17.8</v>
       </c>
-      <c r="S43" s="3" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="T43" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="U43" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="V43" s="11" t="n">
-        <v>22.4</v>
+      <c r="S43" s="9" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="T43" s="9" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="U43" s="9" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="V43" s="9" t="n">
+        <v>21.4</v>
       </c>
       <c r="W43" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="X43" s="11" t="n">
-        <v>120.9</v>
-      </c>
-      <c r="Y43" s="3" t="n">
-        <v>239.2</v>
-      </c>
-      <c r="Z43" s="3" t="n">
-        <v>113</v>
+      <c r="X43" s="9" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="Y43" s="9" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="Z43" s="9" t="n">
+        <v>7.3</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4158,24 +4173,24 @@
         <v>0.1</v>
       </c>
       <c r="D44" s="9" t="inlineStr"/>
-      <c r="E44" s="15" t="inlineStr"/>
-      <c r="F44" s="15" t="inlineStr"/>
+      <c r="E44" s="9" t="inlineStr"/>
+      <c r="F44" s="9" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="15" t="inlineStr"/>
-      <c r="L44" s="15" t="inlineStr"/>
-      <c r="M44" s="15" t="inlineStr"/>
+      <c r="K44" s="9" t="inlineStr"/>
+      <c r="L44" s="16" t="inlineStr"/>
+      <c r="M44" s="16" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
       <c r="Q44" s="9" t="inlineStr"/>
-      <c r="R44" s="15" t="inlineStr"/>
+      <c r="R44" s="9" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="15" t="inlineStr"/>
+      <c r="V44" s="9" t="inlineStr"/>
       <c r="W44" s="9" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
@@ -4194,73 +4209,73 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>3119.5</v>
-      </c>
-      <c r="D45" s="12" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="D45" s="9" t="n">
         <v>131.1</v>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="E45" s="10" t="n">
         <v>53.9</v>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="F45" s="9" t="n">
         <v>92.5</v>
       </c>
-      <c r="G45" s="9" t="n">
-        <v>77.2</v>
+      <c r="G45" s="3" t="n">
+        <v>77.5</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>32.9</v>
+        <v>32.4</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>181.9</v>
+        <v>18.9</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>23.2</v>
       </c>
-      <c r="K45" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L45" s="12" t="n">
+      <c r="K45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="10" t="n">
         <v>56.4</v>
       </c>
-      <c r="M45" s="12" t="n">
-        <v>155.9</v>
+      <c r="M45" s="10" t="n">
+        <v>55.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>161.9</v>
+        <v>60.9</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>9498</v>
+        <v>490</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>126.9</v>
-      </c>
-      <c r="R45" s="12" t="n">
+        <v>126.3</v>
+      </c>
+      <c r="R45" s="9" t="n">
         <v>89.2</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>81.8</v>
+        <v>81.5</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>282.5</v>
+        <v>252.5</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>79.8</v>
       </c>
-      <c r="V45" s="12" t="n">
+      <c r="V45" s="9" t="n">
         <v>108.9</v>
       </c>
       <c r="W45" s="9" t="n">
-        <v>82.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>10688.8</v>
+        <v>60.8</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>2302.8</v>
+        <v>302.8</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>20.7</v>
@@ -4284,14 +4299,14 @@
       <c r="D46" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="E46" s="12" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="F46" s="12" t="n">
+      <c r="E46" s="9" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F46" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="G46" s="11" t="n">
-        <v>51.3</v>
+      <c r="G46" s="9" t="n">
+        <v>15.5</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>6.5</v>
@@ -4300,22 +4315,22 @@
         <v>3.8</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="K46" s="11" t="n">
-        <v>1111.9</v>
-      </c>
-      <c r="L46" s="12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K46" s="8" t="n">
+        <v>11111111</v>
+      </c>
+      <c r="L46" s="10" t="n">
         <v>11.3</v>
       </c>
-      <c r="M46" s="12" t="n">
+      <c r="M46" s="10" t="n">
         <v>11.1</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>13.1</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>1.4</v>
@@ -4323,31 +4338,31 @@
       <c r="Q46" s="9" t="n">
         <v>25.3</v>
       </c>
-      <c r="R46" s="12" t="n">
+      <c r="R46" s="9" t="n">
         <v>17.8</v>
       </c>
-      <c r="S46" s="3" t="n">
+      <c r="S46" s="9" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="T46" s="9" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="U46" s="9" t="n">
         <v>11.9</v>
       </c>
-      <c r="T46" s="3" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="U46" s="11" t="n">
-        <v>65.40000000000001</v>
-      </c>
-      <c r="V46" s="12" t="n">
+      <c r="V46" s="9" t="n">
         <v>21.8</v>
       </c>
       <c r="W46" s="9" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="X46" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="X46" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="Y46" s="3" t="n">
-        <v>161.2</v>
-      </c>
-      <c r="Z46" s="3" t="n">
+      <c r="Y46" s="9" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="Z46" s="9" t="n">
         <v>10.1</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_lastcheck.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_lastcheck.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -131,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,25 +146,19 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -786,16 +774,16 @@
       <c r="C4" s="3" t="n">
         <v>289.1</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="8" t="n">
         <v>13.8</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="G4" s="9" t="n">
+      <c r="G4" s="8" t="n">
         <v>12.1</v>
       </c>
       <c r="H4" s="3" t="n">
@@ -810,49 +798,49 @@
       <c r="K4" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="L4" s="9" t="n">
+      <c r="L4" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="M4" s="9" t="n">
+      <c r="M4" s="8" t="n">
         <v>15.9</v>
       </c>
-      <c r="N4" s="9" t="n">
+      <c r="N4" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="O4" s="9" t="n">
+      <c r="O4" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="P4" s="9" t="n">
+      <c r="P4" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q4" s="9" t="n">
+      <c r="Q4" s="8" t="n">
         <v>17.7</v>
       </c>
-      <c r="R4" s="9" t="n">
+      <c r="R4" s="8" t="n">
         <v>17.3</v>
       </c>
-      <c r="S4" s="9" t="n">
+      <c r="S4" s="8" t="n">
         <v>19.7</v>
       </c>
-      <c r="T4" s="9" t="n">
+      <c r="T4" s="8" t="n">
         <v>97.5</v>
       </c>
-      <c r="U4" s="9" t="n">
+      <c r="U4" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="V4" s="9" t="n">
+      <c r="V4" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="W4" s="9" t="n">
+      <c r="W4" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="X4" s="9" t="n">
+      <c r="X4" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="Y4" s="9" t="n">
+      <c r="Y4" s="8" t="n">
         <v>95.09999999999999</v>
       </c>
-      <c r="Z4" s="9" t="n">
+      <c r="Z4" s="8" t="n">
         <v>1</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -871,16 +859,16 @@
       <c r="C5" s="3" t="n">
         <v>464.5</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="8" t="n">
         <v>26.5</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="8" t="n">
         <v>20.3</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="8" t="n">
         <v>12.5</v>
       </c>
       <c r="H5" s="3" t="n">
@@ -898,10 +886,10 @@
       <c r="L5" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="M5" s="9" t="n">
+      <c r="M5" s="8" t="n">
         <v>13.9</v>
       </c>
-      <c r="N5" s="9" t="n">
+      <c r="N5" s="8" t="n">
         <v>15.8</v>
       </c>
       <c r="O5" s="3" t="n">
@@ -910,34 +898,34 @@
       <c r="P5" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q5" s="9" t="n">
+      <c r="Q5" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="R5" s="9" t="n">
+      <c r="R5" s="8" t="n">
         <v>17.9</v>
       </c>
-      <c r="S5" s="9" t="n">
+      <c r="S5" s="8" t="n">
         <v>20.5</v>
       </c>
-      <c r="T5" s="9" t="n">
+      <c r="T5" s="8" t="n">
         <v>81</v>
       </c>
-      <c r="U5" s="9" t="n">
+      <c r="U5" s="8" t="n">
         <v>4.8</v>
       </c>
-      <c r="V5" s="9" t="n">
+      <c r="V5" s="8" t="n">
         <v>20.3</v>
       </c>
-      <c r="W5" s="9" t="n">
+      <c r="W5" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="X5" s="9" t="n">
+      <c r="X5" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="Y5" s="9" t="n">
+      <c r="Y5" s="8" t="n">
         <v>83.40000000000001</v>
       </c>
-      <c r="Z5" s="9" t="n">
+      <c r="Z5" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -956,16 +944,16 @@
       <c r="C6" s="3" t="n">
         <v>338</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="8" t="n">
         <v>14.3</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="8" t="n">
         <v>10.1</v>
       </c>
       <c r="H6" s="3" t="n">
@@ -980,49 +968,49 @@
       <c r="K6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="9" t="n">
+      <c r="L6" s="8" t="n">
         <v>14.3</v>
       </c>
-      <c r="M6" s="9" t="n">
+      <c r="M6" s="8" t="n">
         <v>14.2</v>
       </c>
-      <c r="N6" s="9" t="n">
+      <c r="N6" s="8" t="n">
         <v>16.1</v>
       </c>
-      <c r="O6" s="9" t="n">
+      <c r="O6" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="P6" s="9" t="n">
+      <c r="P6" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q6" s="9" t="n">
+      <c r="Q6" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="R6" s="9" t="n">
+      <c r="R6" s="8" t="n">
         <v>17.9</v>
       </c>
-      <c r="S6" s="9" t="n">
+      <c r="S6" s="8" t="n">
         <v>20.5</v>
       </c>
-      <c r="T6" s="9" t="n">
+      <c r="T6" s="8" t="n">
         <v>76.59999999999999</v>
       </c>
-      <c r="U6" s="9" t="n">
+      <c r="U6" s="8" t="n">
         <v>6.3</v>
       </c>
-      <c r="V6" s="9" t="n">
+      <c r="V6" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="W6" s="9" t="n">
+      <c r="W6" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="X6" s="9" t="n">
+      <c r="X6" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="Y6" s="9" t="n">
+      <c r="Y6" s="8" t="n">
         <v>95.09999999999999</v>
       </c>
-      <c r="Z6" s="9" t="n">
+      <c r="Z6" s="8" t="n">
         <v>1.1</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1041,16 +1029,16 @@
       <c r="C7" s="3" t="n">
         <v>355.7</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="8" t="n">
         <v>14.6</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G7" s="8" t="n">
         <v>10.7</v>
       </c>
       <c r="H7" s="3" t="n">
@@ -1068,46 +1056,46 @@
       <c r="L7" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="M7" s="9" t="n">
+      <c r="M7" s="8" t="n">
         <v>15.2</v>
       </c>
-      <c r="N7" s="9" t="n">
+      <c r="N7" s="8" t="n">
         <v>17.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>98</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q7" s="9" t="n">
+      <c r="Q7" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="R7" s="9" t="n">
+      <c r="R7" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="S7" s="9" t="n">
+      <c r="S7" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="T7" s="9" t="n">
+      <c r="T7" s="8" t="n">
         <v>83.90000000000001</v>
       </c>
-      <c r="U7" s="9" t="n">
+      <c r="U7" s="8" t="n">
         <v>3.8</v>
       </c>
-      <c r="V7" s="9" t="n">
+      <c r="V7" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="W7" s="9" t="n">
+      <c r="W7" s="8" t="n">
         <v>16.1</v>
       </c>
-      <c r="X7" s="9" t="n">
+      <c r="X7" s="8" t="n">
         <v>18.3</v>
       </c>
-      <c r="Y7" s="9" t="n">
+      <c r="Y7" s="8" t="n">
         <v>84</v>
       </c>
-      <c r="Z7" s="9" t="n">
+      <c r="Z7" s="8" t="n">
         <v>3.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1126,16 +1114,16 @@
       <c r="C8" s="3" t="n">
         <v>377.9</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="8" t="n">
         <v>14.8</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="G8" s="9" t="n">
+      <c r="G8" s="8" t="n">
         <v>9.6</v>
       </c>
       <c r="H8" s="3" t="n">
@@ -1150,49 +1138,49 @@
       <c r="K8" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="L8" s="9" t="n">
+      <c r="L8" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="M8" s="9" t="n">
+      <c r="M8" s="8" t="n">
         <v>15.1</v>
       </c>
-      <c r="N8" s="9" t="n">
+      <c r="N8" s="3" t="n">
+        <v>171.9</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q8" s="8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="R8" s="8" t="n">
         <v>17.1</v>
       </c>
-      <c r="O8" s="9" t="n">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="P8" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q8" s="9" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="R8" s="9" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="S8" s="9" t="n">
+      <c r="S8" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="T8" s="9" t="n">
+      <c r="T8" s="8" t="n">
         <v>73</v>
       </c>
-      <c r="U8" s="9" t="n">
+      <c r="U8" s="8" t="n">
         <v>7.2</v>
       </c>
-      <c r="V8" s="9" t="n">
+      <c r="V8" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="W8" s="9" t="n">
+      <c r="W8" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="X8" s="9" t="n">
+      <c r="X8" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="Y8" s="9" t="n">
+      <c r="Y8" s="8" t="n">
         <v>88.2</v>
       </c>
-      <c r="Z8" s="9" t="n">
+      <c r="Z8" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1211,16 +1199,16 @@
       <c r="C9" s="3" t="n">
         <v>1825.2</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="8" t="n">
         <v>126.5</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="8" t="n">
         <v>71.5</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="8" t="n">
         <v>55</v>
       </c>
       <c r="H9" s="3" t="n">
@@ -1232,50 +1220,50 @@
       <c r="J9" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K9" s="10" t="n">
+      <c r="K9" s="9" t="n">
         <v>28.9</v>
       </c>
-      <c r="L9" s="10" t="n">
+      <c r="L9" s="9" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="M9" s="9" t="n">
+      <c r="M9" s="8" t="n">
         <v>74.3</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>84.09999999999999</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>93</v>
+        <v>493</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q9" s="9" t="n">
+      <c r="Q9" s="8" t="n">
         <v>103.3</v>
       </c>
-      <c r="R9" s="10" t="n">
+      <c r="R9" s="9" t="n">
         <v>89.90000000000001</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>95.59999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>895.5</v>
+        <v>2.8</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="V9" s="9" t="n">
+      <c r="V9" s="8" t="n">
         <v>95.5</v>
       </c>
-      <c r="W9" s="10" t="n">
+      <c r="W9" s="9" t="n">
         <v>87.2</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>94.8</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>29</v>
+        <v>429</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>16.1</v>
@@ -1296,16 +1284,16 @@
       <c r="C10" s="3" t="n">
         <v>365</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="8" t="n">
         <v>14.3</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="G10" s="8" t="n">
         <v>11</v>
       </c>
       <c r="H10" s="3" t="n">
@@ -1317,52 +1305,52 @@
       <c r="J10" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K10" s="8" t="n">
-        <v>1100.1</v>
-      </c>
-      <c r="L10" s="10" t="n">
+      <c r="K10" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L10" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="M10" s="9" t="n">
+      <c r="M10" s="8" t="n">
         <v>14.9</v>
       </c>
-      <c r="N10" s="9" t="n">
+      <c r="N10" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="O10" s="9" t="n">
+      <c r="O10" s="8" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="P10" s="9" t="n">
+      <c r="P10" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q10" s="9" t="n">
+      <c r="Q10" s="8" t="n">
         <v>20.7</v>
       </c>
-      <c r="R10" s="10" t="n">
+      <c r="R10" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="S10" s="9" t="n">
+      <c r="S10" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="T10" s="9" t="n">
+      <c r="T10" s="8" t="n">
         <v>84.5</v>
       </c>
-      <c r="U10" s="9" t="n">
+      <c r="U10" s="8" t="n">
         <v>3.8</v>
       </c>
-      <c r="V10" s="9" t="n">
+      <c r="V10" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="W10" s="9" t="n">
+      <c r="W10" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="X10" s="9" t="n">
+      <c r="X10" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="Y10" s="9" t="n">
+      <c r="Y10" s="8" t="n">
         <v>89.90000000000001</v>
       </c>
-      <c r="Z10" s="9" t="n">
+      <c r="Z10" s="8" t="n">
         <v>2.2</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1381,16 +1369,16 @@
       <c r="C11" s="3" t="n">
         <v>324.6</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="8" t="n">
         <v>23.4</v>
       </c>
-      <c r="E11" s="9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="G11" s="3" t="n">
+      <c r="E11" s="8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G11" s="8" t="n">
         <v>10.1</v>
       </c>
       <c r="H11" s="3" t="n">
@@ -1406,12 +1394,12 @@
         <v>17.9</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="M11" s="9" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="M11" s="8" t="n">
         <v>13.7</v>
       </c>
-      <c r="N11" s="9" t="n">
+      <c r="N11" s="8" t="n">
         <v>15.6</v>
       </c>
       <c r="O11" s="3" t="n">
@@ -1420,14 +1408,14 @@
       <c r="P11" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="9" t="n">
+      <c r="Q11" s="8" t="n">
         <v>22.3</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>29.5</v>
+        <v>29.3</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>72</v>
@@ -1435,19 +1423,19 @@
       <c r="U11" s="3" t="n">
         <v>7.4</v>
       </c>
-      <c r="V11" s="9" t="n">
+      <c r="V11" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="W11" s="9" t="n">
+      <c r="W11" s="8" t="n">
         <v>18.1</v>
       </c>
-      <c r="X11" s="9" t="n">
+      <c r="X11" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="Y11" s="9" t="n">
+      <c r="Y11" s="8" t="n">
         <v>96.90000000000001</v>
       </c>
-      <c r="Z11" s="9" t="n">
+      <c r="Z11" s="8" t="n">
         <v>0.7</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1464,18 +1452,18 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="D12" s="9" t="n">
+        <v>511.1</v>
+      </c>
+      <c r="D12" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="8" t="n">
         <v>13.9</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="8" t="n">
         <v>11.8</v>
       </c>
       <c r="H12" s="3" t="n">
@@ -1490,22 +1478,22 @@
       <c r="K12" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L12" s="9" t="n">
+      <c r="L12" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="M12" s="9" t="n">
+      <c r="M12" s="8" t="n">
         <v>14.4</v>
       </c>
-      <c r="N12" s="9" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="O12" s="9" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="P12" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q12" s="9" t="n">
+      <c r="N12" s="8" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q12" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="R12" s="3" t="n">
@@ -1515,24 +1503,24 @@
         <v>16.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>20.1</v>
+        <v>22.2</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="V12" s="9" t="n">
+      <c r="V12" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="W12" s="9" t="n">
+      <c r="W12" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="X12" s="9" t="n">
+      <c r="X12" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="Y12" s="9" t="n">
+      <c r="Y12" s="8" t="n">
         <v>85</v>
       </c>
-      <c r="Z12" s="9" t="n">
+      <c r="Z12" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -1551,13 +1539,13 @@
       <c r="C13" s="3" t="n">
         <v>455.6</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="8" t="n">
         <v>11.6</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="8" t="n">
         <v>18.1</v>
       </c>
       <c r="G13" s="3" t="n">
@@ -1575,49 +1563,49 @@
       <c r="K13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="L13" s="8" t="n">
         <v>11.7</v>
       </c>
-      <c r="M13" s="9" t="n">
+      <c r="M13" s="8" t="n">
         <v>11.6</v>
       </c>
-      <c r="N13" s="9" t="n">
+      <c r="N13" s="8" t="n">
         <v>13.5</v>
       </c>
-      <c r="O13" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Q13" s="9" t="n">
+      <c r="O13" s="8" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="P13" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q13" s="8" t="n">
         <v>23.8</v>
       </c>
-      <c r="R13" s="9" t="n">
+      <c r="R13" s="8" t="n">
         <v>17.3</v>
       </c>
-      <c r="S13" s="9" t="n">
+      <c r="S13" s="8" t="n">
         <v>19.7</v>
       </c>
-      <c r="T13" s="9" t="n">
+      <c r="T13" s="8" t="n">
         <v>66.8</v>
       </c>
-      <c r="U13" s="9" t="n">
+      <c r="U13" s="8" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V13" s="9" t="n">
+      <c r="V13" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="W13" s="9" t="n">
+      <c r="W13" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="X13" s="9" t="n">
+      <c r="X13" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="Y13" s="9" t="n">
+      <c r="Y13" s="8" t="n">
         <v>83</v>
       </c>
-      <c r="Z13" s="9" t="n">
+      <c r="Z13" s="8" t="n">
         <v>4.2</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -1636,16 +1624,16 @@
       <c r="C14" s="3" t="n">
         <v>531.1</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="8" t="n">
         <v>12.3</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="G14" s="9" t="n">
+      <c r="G14" s="8" t="n">
         <v>14.5</v>
       </c>
       <c r="H14" s="3" t="n">
@@ -1660,22 +1648,22 @@
       <c r="K14" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" s="8" t="n">
         <v>12.5</v>
       </c>
-      <c r="M14" s="9" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="N14" s="9" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="O14" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P14" s="3" t="n">
+      <c r="M14" s="8" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="N14" s="8" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="O14" s="8" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P14" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q14" s="9" t="n">
+      <c r="Q14" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="R14" s="3" t="n">
@@ -1690,19 +1678,19 @@
       <c r="U14" s="3" t="n">
         <v>7.8</v>
       </c>
-      <c r="V14" s="9" t="n">
+      <c r="V14" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="W14" s="9" t="n">
+      <c r="W14" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="X14" s="9" t="n">
+      <c r="X14" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="Y14" s="9" t="n">
+      <c r="Y14" s="8" t="n">
         <v>87.2</v>
       </c>
-      <c r="Z14" s="9" t="n">
+      <c r="Z14" s="8" t="n">
         <v>3.1</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -1721,23 +1709,23 @@
       <c r="C15" s="3" t="n">
         <v>484.5</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="8" t="n">
         <v>26.7</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="8" t="n">
         <v>14.1</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="G15" s="3" t="n">
-        <v>22.6</v>
+      <c r="G15" s="8" t="n">
+        <v>12.6</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>10.7</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>2.4</v>
+        <v>21.4</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.2</v>
@@ -1748,10 +1736,10 @@
       <c r="L15" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="M15" s="9" t="n">
+      <c r="M15" s="8" t="n">
         <v>14.1</v>
       </c>
-      <c r="N15" s="9" t="n">
+      <c r="N15" s="8" t="n">
         <v>15.9</v>
       </c>
       <c r="O15" s="3" t="n">
@@ -1760,34 +1748,34 @@
       <c r="P15" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q15" s="9" t="n">
+      <c r="Q15" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="R15" s="9" t="n">
+      <c r="R15" s="8" t="n">
         <v>13.9</v>
       </c>
-      <c r="S15" s="9" t="n">
+      <c r="S15" s="8" t="n">
         <v>15.9</v>
       </c>
-      <c r="T15" s="9" t="n">
+      <c r="T15" s="8" t="n">
         <v>48</v>
       </c>
-      <c r="U15" s="9" t="n">
+      <c r="U15" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="V15" s="9" t="n">
+      <c r="V15" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="W15" s="9" t="n">
+      <c r="W15" s="8" t="n">
         <v>17.3</v>
       </c>
-      <c r="X15" s="9" t="n">
+      <c r="X15" s="8" t="n">
         <v>19.7</v>
       </c>
-      <c r="Y15" s="9" t="n">
+      <c r="Y15" s="8" t="n">
         <v>88.8</v>
       </c>
-      <c r="Z15" s="9" t="n">
+      <c r="Z15" s="8" t="n">
         <v>2.5</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -1806,16 +1794,16 @@
       <c r="C16" s="3" t="n">
         <v>230.6</v>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="D16" s="8" t="n">
         <v>127.2</v>
       </c>
-      <c r="E16" s="10" t="n">
+      <c r="E16" s="8" t="n">
         <v>65.2</v>
       </c>
-      <c r="F16" s="10" t="n">
+      <c r="F16" s="8" t="n">
         <v>96.2</v>
       </c>
-      <c r="G16" s="9" t="n">
+      <c r="G16" s="8" t="n">
         <v>62</v>
       </c>
       <c r="H16" s="3" t="n">
@@ -1827,48 +1815,48 @@
       <c r="J16" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="K16" s="10" t="n">
+      <c r="K16" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="L16" s="10" t="n">
+      <c r="L16" s="9" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="M16" s="9" t="n">
-        <v>66.5</v>
+      <c r="M16" s="8" t="n">
+        <v>66.2</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>45.6</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>95</v>
+        <v>493</v>
       </c>
       <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="9" t="n">
+      <c r="Q16" s="8" t="n">
         <v>118.7</v>
       </c>
-      <c r="R16" s="10" t="n">
+      <c r="R16" s="9" t="n">
         <v>92.40000000000001</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>91.59999999999999</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>13</v>
+        <v>313</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>55.8</v>
       </c>
-      <c r="V16" s="9" t="n">
+      <c r="V16" s="8" t="n">
         <v>100.4</v>
       </c>
-      <c r="W16" s="10" t="n">
+      <c r="W16" s="9" t="n">
         <v>90.90000000000001</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>99.8</v>
+        <v>99.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>24</v>
+        <v>424</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>18.4</v>
@@ -1887,18 +1875,18 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="D17" s="9" t="n">
+        <v>461.4</v>
+      </c>
+      <c r="D17" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="E17" s="10" t="n">
+      <c r="E17" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="F17" s="10" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="G17" s="9" t="n">
+      <c r="F17" s="8" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="G17" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="H17" s="3" t="n">
@@ -1913,10 +1901,10 @@
       <c r="K17" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="L17" s="10" t="n">
+      <c r="L17" s="9" t="n">
         <v>13.4</v>
       </c>
-      <c r="M17" s="9" t="n">
+      <c r="M17" s="8" t="n">
         <v>13.2</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1928,10 +1916,10 @@
       <c r="P17" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q17" s="9" t="n">
+      <c r="Q17" s="8" t="n">
         <v>23.7</v>
       </c>
-      <c r="R17" s="10" t="n">
+      <c r="R17" s="9" t="n">
         <v>18.5</v>
       </c>
       <c r="S17" s="3" t="n">
@@ -1943,19 +1931,19 @@
       <c r="U17" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="V17" s="9" t="n">
+      <c r="V17" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="W17" s="9" t="n">
+      <c r="W17" s="8" t="n">
         <v>18.2</v>
       </c>
-      <c r="X17" s="9" t="n">
+      <c r="X17" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="Y17" s="9" t="n">
+      <c r="Y17" s="8" t="n">
         <v>88.8</v>
       </c>
-      <c r="Z17" s="9" t="n">
+      <c r="Z17" s="8" t="n">
         <v>2.6</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -1974,16 +1962,16 @@
       <c r="C18" s="3" t="n">
         <v>355.7</v>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="D18" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="8" t="n">
         <v>14.3</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="G18" s="9" t="n">
+      <c r="G18" s="8" t="n">
         <v>9.6</v>
       </c>
       <c r="H18" s="3" t="n">
@@ -1995,52 +1983,52 @@
       <c r="J18" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="L18" s="9" t="n">
+      <c r="L18" s="8" t="n">
         <v>14.2</v>
       </c>
-      <c r="M18" s="9" t="n">
+      <c r="M18" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="N18" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="O18" s="9" t="n">
-        <v>98.7</v>
-      </c>
-      <c r="P18" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q18" s="9" t="n">
+      <c r="N18" s="8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="O18" s="8" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="P18" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q18" s="8" t="n">
         <v>22.4</v>
       </c>
-      <c r="R18" s="9" t="n">
+      <c r="R18" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="S18" s="9" t="n">
+      <c r="S18" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="T18" s="9" t="n">
+      <c r="T18" s="8" t="n">
         <v>74</v>
       </c>
-      <c r="U18" s="9" t="n">
+      <c r="U18" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="V18" s="9" t="n">
+      <c r="V18" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="W18" s="9" t="n">
+      <c r="W18" s="8" t="n">
         <v>14.1</v>
       </c>
-      <c r="X18" s="9" t="n">
+      <c r="X18" s="8" t="n">
         <v>16.1</v>
       </c>
-      <c r="Y18" s="9" t="n">
+      <c r="Y18" s="8" t="n">
         <v>68</v>
       </c>
-      <c r="Z18" s="9" t="n">
+      <c r="Z18" s="8" t="n">
         <v>7.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2057,18 +2045,18 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>235.6</v>
-      </c>
-      <c r="D19" s="9" t="n">
+        <v>2135.6</v>
+      </c>
+      <c r="D19" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="G19" s="9" t="n">
+      <c r="G19" s="8" t="n">
         <v>12.7</v>
       </c>
       <c r="H19" s="3" t="n">
@@ -2080,52 +2068,52 @@
       <c r="J19" s="3" t="n">
         <v>4.3</v>
       </c>
-      <c r="K19" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L19" s="9" t="n">
+      <c r="K19" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L19" s="8" t="n">
         <v>14.2</v>
       </c>
-      <c r="M19" s="9" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="N19" s="9" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="O19" s="9" t="n">
-        <v>91.3</v>
-      </c>
-      <c r="P19" s="9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q19" s="9" t="n">
+      <c r="M19" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q19" s="8" t="n">
         <v>24.5</v>
       </c>
-      <c r="R19" s="9" t="n">
+      <c r="R19" s="8" t="n">
         <v>18.2</v>
       </c>
-      <c r="S19" s="9" t="n">
+      <c r="S19" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="T19" s="9" t="n">
+      <c r="T19" s="8" t="n">
         <v>67.90000000000001</v>
       </c>
-      <c r="U19" s="9" t="n">
+      <c r="U19" s="8" t="n">
         <v>9.9</v>
       </c>
-      <c r="V19" s="9" t="n">
+      <c r="V19" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="W19" s="9" t="n">
+      <c r="W19" s="8" t="n">
         <v>16.6</v>
       </c>
-      <c r="X19" s="9" t="n">
+      <c r="X19" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="Y19" s="9" t="n">
+      <c r="Y19" s="8" t="n">
         <v>84</v>
       </c>
-      <c r="Z19" s="9" t="n">
+      <c r="Z19" s="8" t="n">
         <v>3.6</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -2142,18 +2130,18 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="D20" s="9" t="n">
+        <v>417.9</v>
+      </c>
+      <c r="D20" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="8" t="n">
         <v>12.4</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="G20" s="9" t="n">
+      <c r="G20" s="8" t="n">
         <v>14.8</v>
       </c>
       <c r="H20" s="3" t="n">
@@ -2165,52 +2153,52 @@
       <c r="J20" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="L20" s="9" t="n">
+      <c r="L20" s="8" t="n">
         <v>12.6</v>
       </c>
-      <c r="M20" s="9" t="n">
+      <c r="M20" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="N20" s="9" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="O20" s="9" t="n">
-        <v>98.7</v>
-      </c>
-      <c r="P20" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q20" s="9" t="n">
+      <c r="N20" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>184.4</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q20" s="8" t="n">
         <v>23.4</v>
       </c>
-      <c r="R20" s="9" t="n">
+      <c r="R20" s="8" t="n">
         <v>17.5</v>
       </c>
-      <c r="S20" s="9" t="n">
+      <c r="S20" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="T20" s="9" t="n">
+      <c r="T20" s="8" t="n">
         <v>69.5</v>
       </c>
-      <c r="U20" s="9" t="n">
+      <c r="U20" s="8" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="V20" s="9" t="n">
+      <c r="V20" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="W20" s="9" t="n">
+      <c r="W20" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="X20" s="9" t="n">
+      <c r="X20" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="Y20" s="9" t="n">
+      <c r="Y20" s="8" t="n">
         <v>87</v>
       </c>
-      <c r="Z20" s="9" t="n">
+      <c r="Z20" s="8" t="n">
         <v>2.9</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -2229,16 +2217,16 @@
       <c r="C21" s="3" t="n">
         <v>371.3</v>
       </c>
-      <c r="D21" s="9" t="n">
+      <c r="D21" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E21" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="F21" s="9" t="n">
+      <c r="F21" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="G21" s="9" t="n">
+      <c r="G21" s="8" t="n">
         <v>11.6</v>
       </c>
       <c r="H21" s="3" t="n">
@@ -2250,53 +2238,53 @@
       <c r="J21" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="L21" s="9" t="n">
+      <c r="L21" s="8" t="n">
         <v>16.5</v>
       </c>
-      <c r="M21" s="9" t="n">
+      <c r="M21" s="8" t="n">
         <v>16.5</v>
       </c>
-      <c r="N21" s="9" t="n">
+      <c r="N21" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="O21" s="9" t="n">
+      <c r="O21" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="P21" s="9" t="n">
+      <c r="P21" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" s="9" t="n">
+      <c r="Q21" s="8" t="n">
         <v>20.7</v>
       </c>
-      <c r="R21" s="9" t="n">
+      <c r="R21" s="8" t="n">
         <v>18.1</v>
       </c>
-      <c r="S21" s="9" t="n">
+      <c r="S21" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="T21" s="9" t="n">
+      <c r="T21" s="8" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="U21" s="9" t="n">
+      <c r="U21" s="8" t="n">
         <v>3.6</v>
       </c>
-      <c r="V21" s="9" t="n">
+      <c r="V21" s="8" t="n">
         <v>16.6</v>
       </c>
-      <c r="W21" s="9" t="n">
+      <c r="W21" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="X21" s="9" t="n">
+      <c r="X21" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="Y21" s="9" t="n">
-        <v>98.7</v>
-      </c>
-      <c r="Z21" s="9" t="n">
-        <v>0.2</v>
+      <c r="Y21" s="8" t="n">
+        <v>98</v>
+      </c>
+      <c r="Z21" s="8" t="n">
+        <v>0.4</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2314,16 +2302,16 @@
       <c r="C22" s="3" t="n">
         <v>508.9</v>
       </c>
-      <c r="D22" s="9" t="n">
+      <c r="D22" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="8" t="n">
         <v>13.1</v>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F22" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="G22" s="9" t="n">
+      <c r="G22" s="8" t="n">
         <v>12.7</v>
       </c>
       <c r="H22" s="3" t="n">
@@ -2335,52 +2323,52 @@
       <c r="J22" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="8" t="n">
         <v>5.7</v>
       </c>
-      <c r="L22" s="9" t="n">
+      <c r="L22" s="8" t="n">
         <v>13.2</v>
       </c>
-      <c r="M22" s="9" t="n">
+      <c r="M22" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="N22" s="9" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="O22" s="9" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="P22" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q22" s="9" t="n">
+      <c r="N22" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q22" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="R22" s="9" t="n">
+      <c r="R22" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="S22" s="9" t="n">
+      <c r="S22" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="T22" s="9" t="n">
+      <c r="T22" s="8" t="n">
         <v>69.7</v>
       </c>
-      <c r="U22" s="9" t="n">
+      <c r="U22" s="8" t="n">
         <v>9.4</v>
       </c>
-      <c r="V22" s="9" t="n">
+      <c r="V22" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="W22" s="9" t="n">
+      <c r="W22" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="X22" s="9" t="n">
+      <c r="X22" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="Y22" s="9" t="n">
+      <c r="Y22" s="8" t="n">
         <v>94.5</v>
       </c>
-      <c r="Z22" s="9" t="n">
+      <c r="Z22" s="8" t="n">
         <v>1.2</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -2397,18 +2385,18 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>208.9</v>
-      </c>
-      <c r="D23" s="9" t="n">
+        <v>2089.4</v>
+      </c>
+      <c r="D23" s="8" t="n">
         <v>128.2</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="8" t="n">
         <v>66.8</v>
       </c>
-      <c r="F23" s="9" t="n">
+      <c r="F23" s="8" t="n">
         <v>97.5</v>
       </c>
-      <c r="G23" s="9" t="n">
+      <c r="G23" s="8" t="n">
         <v>61.4</v>
       </c>
       <c r="H23" s="3" t="n">
@@ -2418,16 +2406,16 @@
         <v>1.3</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="K23" s="10" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="K23" s="8" t="n">
         <v>27.4</v>
       </c>
-      <c r="L23" s="9" t="n">
+      <c r="L23" s="8" t="n">
         <v>70.7</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>68.59999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>7.9</v>
@@ -2438,10 +2426,10 @@
       <c r="P23" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q23" s="9" t="n">
+      <c r="Q23" s="8" t="n">
         <v>115.6</v>
       </c>
-      <c r="R23" s="10" t="n">
+      <c r="R23" s="9" t="n">
         <v>91.5</v>
       </c>
       <c r="S23" s="3" t="inlineStr"/>
@@ -2451,17 +2439,17 @@
       <c r="U23" s="3" t="n">
         <v>49.8</v>
       </c>
-      <c r="V23" s="9" t="n">
+      <c r="V23" s="8" t="n">
         <v>94.3</v>
       </c>
-      <c r="W23" s="10" t="n">
+      <c r="W23" s="9" t="n">
         <v>86.3</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>93</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>29</v>
+        <v>429</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>16.3</v>
@@ -2480,18 +2468,18 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="D24" s="9" t="n">
+        <v>417.9</v>
+      </c>
+      <c r="D24" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="8" t="n">
         <v>13.4</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="G24" s="9" t="n">
+      <c r="G24" s="8" t="n">
         <v>12.2</v>
       </c>
       <c r="H24" s="3" t="n">
@@ -2504,51 +2492,51 @@
         <v>3.1</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="8" t="n">
         <v>14.1</v>
       </c>
       <c r="M24" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="N24" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="O24" s="3" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="P24" s="3" t="n">
+      <c r="N24" s="8" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="O24" s="8" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="P24" s="8" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q24" s="9" t="n">
+      <c r="Q24" s="8" t="n">
         <v>23.1</v>
       </c>
-      <c r="R24" s="10" t="n">
+      <c r="R24" s="9" t="n">
         <v>18.3</v>
       </c>
-      <c r="S24" s="9" t="n">
+      <c r="S24" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="T24" s="9" t="n">
+      <c r="T24" s="8" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="U24" s="9" t="n">
+      <c r="U24" s="8" t="n">
         <v>7.2</v>
       </c>
-      <c r="V24" s="9" t="n">
+      <c r="V24" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="W24" s="10" t="n">
+      <c r="W24" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="X24" s="9" t="n">
+      <c r="X24" s="8" t="n">
         <v>19.7</v>
       </c>
-      <c r="Y24" s="9" t="n">
+      <c r="Y24" s="8" t="n">
         <v>90.40000000000001</v>
       </c>
-      <c r="Z24" s="9" t="n">
+      <c r="Z24" s="8" t="n">
         <v>2.1</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -2565,18 +2553,18 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>233.5</v>
-      </c>
-      <c r="D25" s="9" t="n">
+        <v>233.6</v>
+      </c>
+      <c r="D25" s="8" t="n">
         <v>23.1</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="8" t="n">
         <v>15.5</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="G25" s="9" t="n">
+      <c r="G25" s="8" t="n">
         <v>7.6</v>
       </c>
       <c r="H25" s="3" t="n">
@@ -2588,53 +2576,53 @@
       <c r="J25" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" s="8" t="n">
         <v>6.6</v>
       </c>
-      <c r="L25" s="9" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="M25" s="9" t="n">
+      <c r="L25" s="8" t="n">
         <v>16.5</v>
       </c>
-      <c r="N25" s="9" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="O25" s="9" t="n">
+      <c r="M25" s="8" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="O25" s="8" t="n">
         <v>98</v>
       </c>
-      <c r="P25" s="9" t="n">
+      <c r="P25" s="8" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q25" s="9" t="n">
+      <c r="Q25" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="R25" s="9" t="n">
+      <c r="R25" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="S25" s="9" t="n">
+      <c r="S25" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="T25" s="9" t="n">
+      <c r="T25" s="8" t="n">
         <v>92.7</v>
       </c>
-      <c r="U25" s="9" t="n">
+      <c r="U25" s="8" t="n">
         <v>1.5</v>
       </c>
-      <c r="V25" s="9" t="n">
+      <c r="V25" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="W25" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="W25" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="X25" s="9" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="Y25" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="Z25" s="9" t="n">
-        <v>0</v>
+      <c r="X25" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y25" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="Z25" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2652,17 +2640,17 @@
       <c r="C26" s="3" t="n">
         <v>268.3</v>
       </c>
-      <c r="D26" s="9" t="n">
+      <c r="D26" s="8" t="n">
         <v>22.4</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="8" t="n">
         <v>15.3</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="G26" s="9" t="n">
-        <v>7.1</v>
+      <c r="G26" s="3" t="n">
+        <v>71.2</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>13.2</v>
@@ -2673,54 +2661,50 @@
       <c r="J26" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="K26" s="8" t="n">
         <v>17.7</v>
       </c>
-      <c r="L26" s="15" t="n">
-        <v>-15.8</v>
-      </c>
-      <c r="M26" s="15" t="n">
-        <v>-15.8</v>
-      </c>
-      <c r="N26" s="9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O26" s="9" t="n">
+      <c r="L26" s="8" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="M26" s="8" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="N26" s="8" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="O26" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="P26" s="9" t="n">
+      <c r="P26" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" s="9" t="n">
+      <c r="Q26" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="R26" s="9" t="n">
+      <c r="R26" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="S26" s="9" t="n">
+      <c r="S26" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="T26" s="9" t="n">
+      <c r="T26" s="8" t="n">
         <v>95.09999999999999</v>
       </c>
-      <c r="U26" s="9" t="n">
+      <c r="U26" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="V26" s="9" t="n">
+      <c r="V26" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="W26" s="9" t="n">
+      <c r="W26" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="X26" s="9" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="Y26" s="9" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="Z26" s="9" t="n">
-        <v>0.3</v>
-      </c>
+      <c r="X26" s="3" t="inlineStr"/>
+      <c r="Y26" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="Z26" s="3" t="inlineStr"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -2735,18 +2719,18 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="D27" s="9" t="n">
+        <v>435.6</v>
+      </c>
+      <c r="D27" s="8" t="n">
         <v>24.5</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="8" t="n">
         <v>13.3</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="G27" s="9" t="n">
+      <c r="G27" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="H27" s="3" t="n">
@@ -2758,53 +2742,53 @@
       <c r="J27" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="8" t="n">
         <v>13.2</v>
       </c>
-      <c r="L27" s="9" t="n">
+      <c r="L27" s="8" t="n">
         <v>13.5</v>
       </c>
-      <c r="M27" s="9" t="n">
+      <c r="M27" s="8" t="n">
         <v>13.4</v>
       </c>
-      <c r="N27" s="9" t="n">
+      <c r="N27" s="8" t="n">
         <v>15.3</v>
       </c>
-      <c r="O27" s="9" t="n">
+      <c r="O27" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="P27" s="9" t="n">
+      <c r="P27" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q27" s="9" t="n">
+      <c r="Q27" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="R27" s="9" t="n">
+      <c r="R27" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="S27" s="9" t="n">
+      <c r="S27" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="T27" s="9" t="n">
+      <c r="T27" s="8" t="n">
         <v>87</v>
       </c>
-      <c r="U27" s="9" t="n">
+      <c r="U27" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="V27" s="9" t="n">
+      <c r="V27" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="W27" s="9" t="n">
+      <c r="W27" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="X27" s="9" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="Y27" s="9" t="n">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="Z27" s="9" t="n">
-        <v>1.8</v>
+      <c r="X27" s="3" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y27" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="Z27" s="3" t="n">
+        <v>2.8</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2822,16 +2806,16 @@
       <c r="C28" s="3" t="n">
         <v>331.3</v>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="D28" s="8" t="n">
         <v>23.7</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="8" t="n">
         <v>13.8</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="G28" s="9" t="n">
+      <c r="G28" s="8" t="n">
         <v>9.9</v>
       </c>
       <c r="H28" s="3" t="n">
@@ -2843,13 +2827,13 @@
       <c r="J28" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="8" t="n">
         <v>32.8</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="M28" s="9" t="n">
+      <c r="M28" s="8" t="n">
         <v>14.3</v>
       </c>
       <c r="N28" s="3" t="n">
@@ -2861,34 +2845,34 @@
       <c r="P28" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q28" s="9" t="n">
+      <c r="Q28" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="R28" s="9" t="n">
+      <c r="R28" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="S28" s="9" t="n">
+      <c r="S28" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="T28" s="9" t="n">
+      <c r="T28" s="8" t="n">
         <v>84.90000000000001</v>
       </c>
-      <c r="U28" s="9" t="n">
+      <c r="U28" s="8" t="n">
         <v>3.4</v>
       </c>
-      <c r="V28" s="9" t="n">
+      <c r="V28" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="W28" s="9" t="n">
+      <c r="W28" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="X28" s="9" t="n">
+      <c r="X28" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="Y28" s="9" t="n">
+      <c r="Y28" s="8" t="n">
         <v>98</v>
       </c>
-      <c r="Z28" s="9" t="n">
+      <c r="Z28" s="8" t="n">
         <v>0.4</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -2907,16 +2891,16 @@
       <c r="C29" s="3" t="n">
         <v>309.1</v>
       </c>
-      <c r="D29" s="9" t="n">
+      <c r="D29" s="8" t="n">
         <v>23.1</v>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="E29" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F29" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="G29" s="9" t="n">
+      <c r="G29" s="8" t="n">
         <v>9.1</v>
       </c>
       <c r="H29" s="3" t="n">
@@ -2928,13 +2912,13 @@
       <c r="J29" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="K29" s="3" t="n">
-        <v>6</v>
+      <c r="K29" s="8" t="n">
+        <v>6.6</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="M29" s="9" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M29" s="8" t="n">
         <v>15</v>
       </c>
       <c r="N29" s="3" t="n">
@@ -2946,35 +2930,35 @@
       <c r="P29" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q29" s="9" t="n">
+      <c r="Q29" s="8" t="n">
         <v>23.6</v>
       </c>
-      <c r="R29" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="S29" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="T29" s="9" t="n">
-        <v>75.40000000000001</v>
-      </c>
-      <c r="U29" s="9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="V29" s="9" t="n">
+      <c r="R29" s="8" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="S29" s="8" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="V29" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="W29" s="9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X29" s="9" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="Y29" s="9" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="Z29" s="9" t="n">
-        <v>0.3</v>
+      <c r="W29" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="Y29" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="Z29" s="3" t="n">
+        <v>0.6</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2992,16 +2976,16 @@
       <c r="C30" s="3" t="n">
         <v>156.9</v>
       </c>
-      <c r="D30" s="9" t="n">
-        <v>116.8</v>
-      </c>
-      <c r="E30" s="9" t="n">
+      <c r="D30" s="8" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="E30" s="8" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="F30" s="9" t="n">
+      <c r="F30" s="8" t="n">
         <v>94.3</v>
       </c>
-      <c r="G30" s="9" t="n">
+      <c r="G30" s="8" t="n">
         <v>44.9</v>
       </c>
       <c r="H30" s="3" t="n">
@@ -3013,39 +2997,39 @@
       <c r="J30" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="K30" s="10" t="n">
+      <c r="K30" s="8" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="L30" s="10" t="n">
+      <c r="L30" s="9" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="M30" s="10" t="n">
+      <c r="M30" s="9" t="n">
         <v>74.3</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>494.8</v>
       </c>
       <c r="P30" s="3" t="inlineStr"/>
-      <c r="Q30" s="9" t="n">
+      <c r="Q30" s="8" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="R30" s="10" t="n">
+      <c r="R30" s="9" t="n">
         <v>89.2</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>95.40000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>13.1</v>
+        <v>413.1</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="V30" s="9" t="n">
-        <v>84.59999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="W30" s="9" t="n">
         <v>82.40000000000001</v>
@@ -3054,7 +3038,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>5.4</v>
@@ -3075,17 +3059,17 @@
       <c r="C31" s="3" t="n">
         <v>314</v>
       </c>
-      <c r="D31" s="9" t="n">
+      <c r="D31" s="8" t="n">
         <v>23.4</v>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E31" s="8" t="n">
         <v>14.4</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="G31" s="9" t="n">
-        <v>9</v>
+      <c r="G31" s="3" t="n">
+        <v>90.40000000000001</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>12.5</v>
@@ -3097,14 +3081,14 @@
         <v>0.9</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="10" t="n">
+      <c r="L31" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="M31" s="10" t="n">
-        <v>14.9</v>
+      <c r="M31" s="9" t="n">
+        <v>13.7</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.1</v>
+        <v>8.1</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>22.8</v>
@@ -3112,35 +3096,35 @@
       <c r="P31" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="Q31" s="9" t="n">
+      <c r="Q31" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="R31" s="10" t="n">
+      <c r="R31" s="9" t="n">
         <v>17.8</v>
       </c>
-      <c r="S31" s="9" t="n">
+      <c r="S31" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="T31" s="9" t="n">
+      <c r="T31" s="8" t="n">
         <v>87.7</v>
       </c>
-      <c r="U31" s="9" t="n">
+      <c r="U31" s="8" t="n">
         <v>2.9</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>17</v>
+        <v>170.4</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="X31" s="9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Y31" s="9" t="n">
-        <v>95.59999999999999</v>
-      </c>
-      <c r="Z31" s="9" t="n">
-        <v>0.8</v>
+      <c r="X31" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="Y31" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="Z31" s="3" t="n">
+        <v>16.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3158,16 +3142,16 @@
       <c r="C32" s="3" t="n">
         <v>364.6</v>
       </c>
-      <c r="D32" s="9" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="E32" s="9" t="n">
+      <c r="D32" s="8" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E32" s="8" t="n">
         <v>11.4</v>
       </c>
-      <c r="F32" s="9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G32" s="9" t="n">
+      <c r="F32" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="G32" s="8" t="n">
         <v>14.3</v>
       </c>
       <c r="H32" s="3" t="n">
@@ -3179,52 +3163,52 @@
       <c r="J32" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="K32" s="9" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="L32" s="9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="M32" s="9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="N32" s="9" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="O32" s="9" t="n">
-        <v>97.40000000000001</v>
-      </c>
-      <c r="P32" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q32" s="9" t="n">
+      <c r="K32" s="3" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="L32" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q32" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="R32" s="9" t="n">
+      <c r="R32" s="8" t="n">
         <v>14.8</v>
       </c>
-      <c r="S32" s="9" t="n">
+      <c r="S32" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="T32" s="9" t="n">
+      <c r="T32" s="8" t="n">
         <v>98.7</v>
       </c>
-      <c r="U32" s="9" t="n">
+      <c r="U32" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="V32" s="9" t="n">
+      <c r="V32" s="8" t="n">
         <v>16.6</v>
       </c>
-      <c r="W32" s="9" t="n">
+      <c r="W32" s="8" t="n">
         <v>16.2</v>
       </c>
-      <c r="X32" s="9" t="n">
+      <c r="X32" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="Y32" s="9" t="n">
+      <c r="Y32" s="8" t="n">
         <v>97.5</v>
       </c>
-      <c r="Z32" s="9" t="n">
+      <c r="Z32" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -3241,18 +3225,18 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="D33" s="9" t="n">
+        <v>411.2</v>
+      </c>
+      <c r="D33" s="8" t="n">
         <v>23.7</v>
       </c>
-      <c r="E33" s="9" t="n">
+      <c r="E33" s="8" t="n">
         <v>13.7</v>
       </c>
-      <c r="F33" s="9" t="n">
+      <c r="F33" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="G33" s="9" t="n">
+      <c r="G33" s="8" t="n">
         <v>10</v>
       </c>
       <c r="H33" s="3" t="n">
@@ -3264,52 +3248,52 @@
       <c r="J33" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="K33" s="9" t="n">
+      <c r="K33" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="L33" s="9" t="n">
+      <c r="L33" s="8" t="n">
         <v>14.3</v>
       </c>
-      <c r="M33" s="9" t="n">
+      <c r="M33" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="N33" s="9" t="n">
+      <c r="N33" s="3" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q33" s="8" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="R33" s="8" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="S33" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="O33" s="9" t="n">
-        <v>120.4</v>
-      </c>
-      <c r="P33" s="9" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="Q33" s="9" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="R33" s="9" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="S33" s="9" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="T33" s="9" t="n">
-        <v>84</v>
-      </c>
-      <c r="U33" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="V33" s="9" t="n">
+      <c r="T33" s="8" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="V33" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="W33" s="9" t="n">
+      <c r="W33" s="8" t="n">
         <v>16.5</v>
       </c>
-      <c r="X33" s="9" t="n">
+      <c r="X33" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="Y33" s="9" t="n">
+      <c r="Y33" s="8" t="n">
         <v>92.09999999999999</v>
       </c>
-      <c r="Z33" s="9" t="n">
+      <c r="Z33" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -3328,16 +3312,16 @@
       <c r="C34" s="3" t="n">
         <v>211.4</v>
       </c>
-      <c r="D34" s="9" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="E34" s="9" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="F34" s="9" t="n">
+      <c r="D34" s="8" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F34" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="G34" s="8" t="n">
         <v>4.6</v>
       </c>
       <c r="H34" s="3" t="n">
@@ -3349,52 +3333,52 @@
       <c r="J34" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="K34" s="9" t="n">
+      <c r="K34" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="L34" s="9" t="n">
+      <c r="L34" s="8" t="n">
         <v>15.1</v>
       </c>
-      <c r="M34" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="N34" s="9" t="n">
+      <c r="M34" s="13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="N34" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="O34" s="9" t="n">
-        <v>99</v>
-      </c>
-      <c r="P34" s="9" t="n">
+      <c r="O34" s="3" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="P34" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q34" s="9" t="n">
+      <c r="Q34" s="8" t="n">
         <v>16.9</v>
       </c>
-      <c r="R34" s="9" t="n">
+      <c r="R34" s="8" t="n">
         <v>15.8</v>
       </c>
-      <c r="S34" s="9" t="n">
+      <c r="S34" s="8" t="n">
         <v>17.9</v>
       </c>
-      <c r="T34" s="9" t="n">
+      <c r="T34" s="8" t="n">
         <v>93.2</v>
       </c>
-      <c r="U34" s="9" t="n">
+      <c r="U34" s="8" t="n">
         <v>1.3</v>
       </c>
-      <c r="V34" s="9" t="n">
+      <c r="V34" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="W34" s="9" t="n">
+      <c r="W34" s="8" t="n">
         <v>15.2</v>
       </c>
-      <c r="X34" s="9" t="n">
+      <c r="X34" s="8" t="n">
         <v>17.3</v>
       </c>
-      <c r="Y34" s="9" t="n">
+      <c r="Y34" s="8" t="n">
         <v>92.59999999999999</v>
       </c>
-      <c r="Z34" s="9" t="n">
+      <c r="Z34" s="8" t="n">
         <v>1.4</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -3411,18 +3395,18 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>77.8</v>
-      </c>
-      <c r="D35" s="9" t="n">
+        <v>477.8</v>
+      </c>
+      <c r="D35" s="8" t="n">
         <v>24.1</v>
       </c>
-      <c r="E35" s="9" t="n">
+      <c r="E35" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="8" t="n">
         <v>18.1</v>
       </c>
-      <c r="G35" s="9" t="n">
+      <c r="G35" s="8" t="n">
         <v>12.1</v>
       </c>
       <c r="H35" s="3" t="n">
@@ -3434,52 +3418,52 @@
       <c r="J35" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K35" s="9" t="n">
+      <c r="K35" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L35" s="9" t="n">
+      <c r="L35" s="8" t="n">
         <v>12.5</v>
       </c>
-      <c r="M35" s="9" t="n">
+      <c r="M35" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="N35" s="9" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="O35" s="9" t="n">
-        <v>98.7</v>
-      </c>
-      <c r="P35" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q35" s="9" t="n">
+      <c r="N35" s="3" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q35" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="R35" s="9" t="n">
+      <c r="R35" s="8" t="n">
         <v>18.3</v>
       </c>
-      <c r="S35" s="9" t="n">
+      <c r="S35" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="T35" s="9" t="n">
+      <c r="T35" s="8" t="n">
         <v>70.90000000000001</v>
       </c>
-      <c r="U35" s="9" t="n">
+      <c r="U35" s="8" t="n">
         <v>8.6</v>
       </c>
-      <c r="V35" s="9" t="n">
+      <c r="V35" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="W35" s="9" t="n">
+      <c r="W35" s="8" t="n">
         <v>15.6</v>
       </c>
-      <c r="X35" s="9" t="n">
+      <c r="X35" s="8" t="n">
         <v>17.7</v>
       </c>
-      <c r="Y35" s="9" t="n">
+      <c r="Y35" s="8" t="n">
         <v>84</v>
       </c>
-      <c r="Z35" s="9" t="n">
+      <c r="Z35" s="8" t="n">
         <v>3.4</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -3496,18 +3480,18 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="D36" s="9" t="n">
+        <v>613.2</v>
+      </c>
+      <c r="D36" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="E36" s="9" t="n">
+      <c r="E36" s="8" t="n">
         <v>13.9</v>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="F36" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="G36" s="9" t="n">
+      <c r="G36" s="8" t="n">
         <v>11.3</v>
       </c>
       <c r="H36" s="3" t="n">
@@ -3519,52 +3503,52 @@
       <c r="J36" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="K36" s="9" t="n">
+      <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="9" t="n">
+      <c r="L36" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="M36" s="9" t="n">
+      <c r="M36" s="8" t="n">
         <v>14.6</v>
       </c>
-      <c r="N36" s="9" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="O36" s="9" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="P36" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q36" s="9" t="n">
+      <c r="N36" s="8" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="O36" s="8" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="P36" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q36" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="R36" s="9" t="n">
+      <c r="R36" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="S36" s="9" t="n">
+      <c r="S36" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="T36" s="9" t="n">
+      <c r="T36" s="8" t="n">
         <v>67.40000000000001</v>
       </c>
-      <c r="U36" s="9" t="n">
+      <c r="U36" s="8" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="V36" s="9" t="n">
+      <c r="V36" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="W36" s="9" t="n">
+      <c r="W36" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="X36" s="9" t="n">
+      <c r="X36" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="Y36" s="9" t="n">
+      <c r="Y36" s="8" t="n">
         <v>79.90000000000001</v>
       </c>
-      <c r="Z36" s="9" t="n">
+      <c r="Z36" s="8" t="n">
         <v>4.9</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -3581,19 +3565,19 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="D37" s="10" t="n">
+        <v>207.8</v>
+      </c>
+      <c r="D37" s="8" t="n">
         <v>118.4</v>
       </c>
-      <c r="E37" s="10" t="n">
+      <c r="E37" s="8" t="n">
         <v>66.09999999999999</v>
       </c>
-      <c r="F37" s="9" t="n">
+      <c r="F37" s="8" t="n">
         <v>92.2</v>
       </c>
-      <c r="G37" s="9" t="n">
-        <v>52.3</v>
+      <c r="G37" s="3" t="n">
+        <v>32.3</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>56.7</v>
@@ -3607,11 +3591,11 @@
       <c r="K37" s="9" t="n">
         <v>50.1</v>
       </c>
-      <c r="L37" s="9" t="n">
-        <v>68.40000000000001</v>
+      <c r="L37" s="8" t="n">
+        <v>68.5</v>
       </c>
       <c r="M37" s="9" t="n">
-        <v>70.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>77.09999999999999</v>
@@ -3620,9 +3604,9 @@
         <v>492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q37" s="9" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="Q37" s="8" t="n">
         <v>101</v>
       </c>
       <c r="R37" s="9" t="n">
@@ -3632,15 +3616,15 @@
         <v>88.09999999999999</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>380.9</v>
+        <v>3809.1</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>33.2</v>
       </c>
-      <c r="V37" s="9" t="n">
+      <c r="V37" s="8" t="n">
         <v>90</v>
       </c>
-      <c r="W37" s="10" t="n">
+      <c r="W37" s="9" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3664,18 +3648,18 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="D38" s="10" t="n">
+        <v>415.6</v>
+      </c>
+      <c r="D38" s="8" t="n">
         <v>23.6</v>
       </c>
-      <c r="E38" s="10" t="n">
+      <c r="E38" s="8" t="n">
         <v>13.1</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="G38" s="9" t="n">
+      <c r="G38" s="8" t="n">
         <v>10.5</v>
       </c>
       <c r="H38" s="3" t="n">
@@ -3688,51 +3672,51 @@
         <v>2.4</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="8" t="n">
         <v>13.7</v>
       </c>
       <c r="M38" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="N38" s="9" t="n">
+      <c r="N38" s="8" t="n">
         <v>15.5</v>
       </c>
-      <c r="O38" s="9" t="n">
+      <c r="O38" s="8" t="n">
         <v>98.7</v>
       </c>
-      <c r="P38" s="9" t="n">
+      <c r="P38" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q38" s="9" t="n">
+      <c r="Q38" s="8" t="n">
         <v>20.2</v>
       </c>
       <c r="R38" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="S38" s="9" t="n">
+      <c r="S38" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="T38" s="9" t="n">
+      <c r="T38" s="8" t="n">
         <v>81.8</v>
       </c>
-      <c r="U38" s="9" t="n">
+      <c r="U38" s="8" t="n">
         <v>4.3</v>
       </c>
-      <c r="V38" s="9" t="n">
+      <c r="V38" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="W38" s="9" t="n">
+      <c r="W38" s="8" t="n">
         <v>16.3</v>
       </c>
-      <c r="X38" s="9" t="n">
+      <c r="X38" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="Y38" s="9" t="n">
+      <c r="Y38" s="8" t="n">
         <v>89.8</v>
       </c>
-      <c r="Z38" s="9" t="n">
+      <c r="Z38" s="8" t="n">
         <v>2.1</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -3749,18 +3733,18 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="D39" s="9" t="n">
+        <v>624.3</v>
+      </c>
+      <c r="D39" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="E39" s="9" t="n">
+      <c r="E39" s="8" t="n">
         <v>11.1</v>
       </c>
-      <c r="F39" s="9" t="n">
+      <c r="F39" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="G39" s="9" t="n">
+      <c r="G39" s="8" t="n">
         <v>14.8</v>
       </c>
       <c r="H39" s="3" t="n">
@@ -3772,52 +3756,52 @@
       <c r="J39" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="K39" s="9" t="n">
+      <c r="K39" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="M39" s="15" t="n">
+      <c r="M39" s="13" t="n">
         <v>1.1</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q39" s="9" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="R39" s="9" t="n">
+      <c r="Q39" s="8" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="R39" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="S39" s="9" t="n">
+      <c r="S39" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="T39" s="9" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="U39" s="9" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="V39" s="9" t="n">
+      <c r="T39" s="8" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="V39" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="W39" s="9" t="n">
+      <c r="W39" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="X39" s="9" t="n">
+      <c r="X39" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="Y39" s="9" t="n">
+      <c r="Y39" s="8" t="n">
         <v>74.59999999999999</v>
       </c>
-      <c r="Z39" s="9" t="n">
+      <c r="Z39" s="8" t="n">
         <v>6.5</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -3834,18 +3818,18 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="D40" s="9" t="n">
+        <v>637.7</v>
+      </c>
+      <c r="D40" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="E40" s="9" t="n">
+      <c r="E40" s="8" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="F40" s="9" t="n">
+      <c r="F40" s="8" t="n">
         <v>17.9</v>
       </c>
-      <c r="G40" s="9" t="n">
+      <c r="G40" s="8" t="n">
         <v>16.3</v>
       </c>
       <c r="H40" s="3" t="n">
@@ -3857,7 +3841,7 @@
       <c r="J40" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="K40" s="9" t="n">
+      <c r="K40" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
@@ -3873,36 +3857,36 @@
         <v>98</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q40" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q40" s="8" t="n">
         <v>25.4</v>
       </c>
-      <c r="R40" s="9" t="n">
+      <c r="R40" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="S40" s="9" t="n">
+      <c r="S40" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="T40" s="9" t="n">
+      <c r="T40" s="8" t="n">
         <v>62</v>
       </c>
-      <c r="U40" s="9" t="n">
+      <c r="U40" s="8" t="n">
         <v>12.3</v>
       </c>
-      <c r="V40" s="9" t="n">
+      <c r="V40" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="W40" s="9" t="n">
+      <c r="W40" s="8" t="n">
         <v>17.3</v>
       </c>
-      <c r="X40" s="9" t="n">
+      <c r="X40" s="8" t="n">
         <v>19.7</v>
       </c>
-      <c r="Y40" s="9" t="n">
+      <c r="Y40" s="8" t="n">
         <v>73.3</v>
       </c>
-      <c r="Z40" s="9" t="n">
+      <c r="Z40" s="8" t="n">
         <v>7.2</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -3921,16 +3905,16 @@
       <c r="C41" s="3" t="n">
         <v>644.3</v>
       </c>
-      <c r="D41" s="9" t="n">
+      <c r="D41" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="E41" s="9" t="n">
+      <c r="E41" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="F41" s="9" t="n">
+      <c r="F41" s="8" t="n">
         <v>18.1</v>
       </c>
-      <c r="G41" s="9" t="n">
+      <c r="G41" s="8" t="n">
         <v>16.2</v>
       </c>
       <c r="H41" s="3" t="inlineStr"/>
@@ -3938,7 +3922,7 @@
       <c r="J41" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="K41" s="9" t="n">
+      <c r="K41" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
@@ -3948,42 +3932,42 @@
         <v>10.5</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q41" s="9" t="n">
+      <c r="Q41" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="R41" s="9" t="n">
+      <c r="R41" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="S41" s="9" t="n">
+      <c r="S41" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="T41" s="9" t="n">
+      <c r="T41" s="8" t="n">
         <v>61.2</v>
       </c>
-      <c r="U41" s="9" t="n">
+      <c r="U41" s="8" t="n">
         <v>12.4</v>
       </c>
-      <c r="V41" s="9" t="n">
+      <c r="V41" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="W41" s="9" t="n">
+      <c r="W41" s="8" t="n">
         <v>16.2</v>
       </c>
-      <c r="X41" s="9" t="n">
+      <c r="X41" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="Y41" s="9" t="n">
+      <c r="Y41" s="8" t="n">
         <v>70.90000000000001</v>
       </c>
-      <c r="Z41" s="9" t="n">
+      <c r="Z41" s="8" t="n">
         <v>7.5</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -4002,16 +3986,16 @@
       <c r="C42" s="3" t="n">
         <v>608.8</v>
       </c>
-      <c r="D42" s="9" t="n">
+      <c r="D42" s="8" t="n">
         <v>26.9</v>
       </c>
-      <c r="E42" s="9" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="F42" s="9" t="n">
+      <c r="E42" s="8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F42" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="G42" s="9" t="n">
+      <c r="G42" s="8" t="n">
         <v>16.5</v>
       </c>
       <c r="H42" s="3" t="n">
@@ -4023,7 +4007,7 @@
       <c r="J42" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K42" s="9" t="n">
+      <c r="K42" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
@@ -4041,34 +4025,34 @@
       <c r="P42" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q42" s="9" t="n">
+      <c r="Q42" s="8" t="n">
         <v>26.1</v>
       </c>
-      <c r="R42" s="9" t="n">
+      <c r="R42" s="8" t="n">
         <v>18.2</v>
       </c>
-      <c r="S42" s="9" t="n">
+      <c r="S42" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="T42" s="9" t="n">
+      <c r="T42" s="8" t="n">
         <v>61.8</v>
       </c>
-      <c r="U42" s="9" t="n">
+      <c r="U42" s="8" t="n">
         <v>12.9</v>
       </c>
-      <c r="V42" s="9" t="n">
+      <c r="V42" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W42" s="9" t="n">
+      <c r="W42" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="X42" s="9" t="n">
+      <c r="X42" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="Y42" s="9" t="n">
+      <c r="Y42" s="8" t="n">
         <v>72.3</v>
       </c>
-      <c r="Z42" s="9" t="n">
+      <c r="Z42" s="8" t="n">
         <v>7.3</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -4087,16 +4071,16 @@
       <c r="C43" s="3" t="n">
         <v>604.4</v>
       </c>
-      <c r="D43" s="9" t="n">
+      <c r="D43" s="8" t="n">
         <v>26.1</v>
       </c>
-      <c r="E43" s="9" t="n">
+      <c r="E43" s="8" t="n">
         <v>12.4</v>
       </c>
-      <c r="F43" s="9" t="n">
+      <c r="F43" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="G43" s="9" t="n">
+      <c r="G43" s="8" t="n">
         <v>13.7</v>
       </c>
       <c r="H43" s="3" t="n">
@@ -4108,7 +4092,7 @@
       <c r="J43" s="3" t="n">
         <v>5.4</v>
       </c>
-      <c r="K43" s="9" t="n">
+      <c r="K43" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="3" t="n">
@@ -4126,34 +4110,34 @@
       <c r="P43" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q43" s="9" t="n">
+      <c r="Q43" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="R43" s="9" t="n">
+      <c r="R43" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="S43" s="9" t="n">
+      <c r="S43" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="T43" s="9" t="n">
+      <c r="T43" s="8" t="n">
         <v>65.09999999999999</v>
       </c>
-      <c r="U43" s="9" t="n">
+      <c r="U43" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="V43" s="9" t="n">
+      <c r="V43" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="W43" s="9" t="n">
+      <c r="W43" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="X43" s="9" t="n">
+      <c r="X43" s="8" t="n">
         <v>18.2</v>
       </c>
-      <c r="Y43" s="9" t="n">
+      <c r="Y43" s="8" t="n">
         <v>71.3</v>
       </c>
-      <c r="Z43" s="9" t="n">
+      <c r="Z43" s="8" t="n">
         <v>7.3</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -4172,26 +4156,26 @@
       <c r="C44" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D44" s="9" t="inlineStr"/>
-      <c r="E44" s="9" t="inlineStr"/>
-      <c r="F44" s="9" t="inlineStr"/>
+      <c r="D44" s="8" t="inlineStr"/>
+      <c r="E44" s="8" t="inlineStr"/>
+      <c r="F44" s="8" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="9" t="inlineStr"/>
-      <c r="L44" s="16" t="inlineStr"/>
-      <c r="M44" s="16" t="inlineStr"/>
+      <c r="K44" s="8" t="inlineStr"/>
+      <c r="L44" s="14" t="inlineStr"/>
+      <c r="M44" s="14" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="9" t="inlineStr"/>
-      <c r="R44" s="9" t="inlineStr"/>
+      <c r="Q44" s="8" t="inlineStr"/>
+      <c r="R44" s="8" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="9" t="inlineStr"/>
-      <c r="W44" s="9" t="inlineStr"/>
+      <c r="V44" s="8" t="inlineStr"/>
+      <c r="W44" s="8" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4209,15 +4193,15 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>119.5</v>
-      </c>
-      <c r="D45" s="9" t="n">
+        <v>3119.5</v>
+      </c>
+      <c r="D45" s="8" t="n">
         <v>131.1</v>
       </c>
-      <c r="E45" s="10" t="n">
+      <c r="E45" s="9" t="n">
         <v>53.9</v>
       </c>
-      <c r="F45" s="9" t="n">
+      <c r="F45" s="8" t="n">
         <v>92.5</v>
       </c>
       <c r="G45" s="3" t="n">
@@ -4232,28 +4216,28 @@
       <c r="J45" s="3" t="n">
         <v>23.2</v>
       </c>
-      <c r="K45" s="9" t="n">
+      <c r="K45" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L45" s="10" t="n">
+      <c r="L45" s="9" t="n">
         <v>56.4</v>
       </c>
-      <c r="M45" s="10" t="n">
+      <c r="M45" s="9" t="n">
         <v>55.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>60.9</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>490</v>
+        <v>26</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q45" s="9" t="n">
-        <v>126.3</v>
-      </c>
-      <c r="R45" s="9" t="n">
+      <c r="Q45" s="8" t="n">
+        <v>127.3</v>
+      </c>
+      <c r="R45" s="8" t="n">
         <v>89.2</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4265,10 +4249,10 @@
       <c r="U45" s="3" t="n">
         <v>79.8</v>
       </c>
-      <c r="V45" s="9" t="n">
+      <c r="V45" s="8" t="n">
         <v>108.9</v>
       </c>
-      <c r="W45" s="9" t="n">
+      <c r="W45" s="8" t="n">
         <v>83.09999999999999</v>
       </c>
       <c r="X45" s="3" t="n">
@@ -4278,7 +4262,7 @@
         <v>302.8</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>20.7</v>
+        <v>50.7</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4296,16 +4280,16 @@
       <c r="C46" s="3" t="n">
         <v>223.9</v>
       </c>
-      <c r="D46" s="9" t="n">
+      <c r="D46" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="E46" s="9" t="n">
+      <c r="E46" s="8" t="n">
         <v>10.7</v>
       </c>
-      <c r="F46" s="9" t="n">
+      <c r="F46" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="G46" s="9" t="n">
+      <c r="G46" s="8" t="n">
         <v>15.5</v>
       </c>
       <c r="H46" s="3" t="n">
@@ -4317,13 +4301,13 @@
       <c r="J46" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K46" s="8" t="n">
-        <v>11111111</v>
-      </c>
-      <c r="L46" s="10" t="n">
+      <c r="K46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" s="9" t="n">
         <v>11.3</v>
       </c>
-      <c r="M46" s="10" t="n">
+      <c r="M46" s="9" t="n">
         <v>11.1</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4333,36 +4317,36 @@
         <v>90</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q46" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q46" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="R46" s="9" t="n">
+      <c r="R46" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="S46" s="9" t="n">
+      <c r="S46" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="T46" s="9" t="n">
+      <c r="T46" s="8" t="n">
         <v>63.2</v>
       </c>
-      <c r="U46" s="9" t="n">
+      <c r="U46" s="8" t="n">
         <v>11.9</v>
       </c>
-      <c r="V46" s="9" t="n">
+      <c r="V46" s="8" t="n">
         <v>21.8</v>
       </c>
-      <c r="W46" s="9" t="n">
+      <c r="W46" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="X46" s="9" t="n">
+      <c r="X46" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="Y46" s="9" t="n">
+      <c r="Y46" s="8" t="n">
         <v>61.2</v>
       </c>
-      <c r="Z46" s="9" t="n">
+      <c r="Z46" s="8" t="n">
         <v>10.1</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_lastcheck.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_lastcheck.xlsx
@@ -47,14 +47,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
   </fills>
@@ -155,10 +155,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -883,20 +883,20 @@
       <c r="K5" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" s="8" t="n">
         <v>14</v>
       </c>
       <c r="M5" s="8" t="n">
         <v>13.9</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>0.4</v>
+        <v>15.9</v>
+      </c>
+      <c r="O5" s="8" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="P5" s="8" t="n">
+        <v>0.1</v>
       </c>
       <c r="Q5" s="8" t="n">
         <v>21.3</v>
@@ -975,28 +975,28 @@
         <v>14.2</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>99</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="Q6" s="8" t="n">
         <v>22.2</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>17.9</v>
+        <v>15.9</v>
       </c>
       <c r="S6" s="8" t="n">
-        <v>20.5</v>
+        <v>18.1</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>76.59999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>6.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="V6" s="8" t="n">
         <v>18.8</v>
@@ -1053,20 +1053,20 @@
       <c r="K7" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="L7" s="3" t="n">
-        <v>13.4</v>
+      <c r="L7" s="8" t="n">
+        <v>15.4</v>
       </c>
       <c r="M7" s="8" t="n">
         <v>15.2</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>0.4</v>
+        <v>17.3</v>
+      </c>
+      <c r="O7" s="8" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P7" s="8" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q7" s="8" t="n">
         <v>20</v>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>377.9</v>
+        <v>37.7</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>24.4</v>
@@ -1138,19 +1138,19 @@
       <c r="K8" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="8" t="n">
         <v>15.2</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>15.1</v>
       </c>
-      <c r="N8" s="3" t="n">
-        <v>171.9</v>
-      </c>
-      <c r="O8" s="3" t="n">
+      <c r="N8" s="8" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="O8" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="P8" s="3" t="n">
+      <c r="P8" s="8" t="n">
         <v>0.2</v>
       </c>
       <c r="Q8" s="8" t="n">
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1825.2</v>
+        <v>182.5</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>126.5</v>
@@ -1223,7 +1223,7 @@
       <c r="K9" s="9" t="n">
         <v>28.9</v>
       </c>
-      <c r="L9" s="9" t="n">
+      <c r="L9" s="8" t="n">
         <v>74.90000000000001</v>
       </c>
       <c r="M9" s="8" t="n">
@@ -1248,7 +1248,7 @@
         <v>96.59999999999999</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>2.8</v>
+        <v>89.5</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>26.9</v>
@@ -1306,22 +1306,22 @@
         <v>1.9</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="L10" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="L10" s="8" t="n">
         <v>15</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>14.9</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>98.59999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="P10" s="8" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="Q10" s="8" t="n">
         <v>20.7</v>
@@ -1394,12 +1394,12 @@
         <v>17.9</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="M11" s="8" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="N11" s="8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="N11" s="3" t="n">
         <v>15.6</v>
       </c>
       <c r="O11" s="3" t="n">
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>511.1</v>
+        <v>51.1</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>25.7</v>
@@ -1481,17 +1481,17 @@
       <c r="L12" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="M12" s="8" t="n">
+      <c r="M12" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="N12" s="8" t="n">
-        <v>16.2</v>
+      <c r="N12" s="3" t="n">
+        <v>16.3</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q12" s="8" t="n">
         <v>24.3</v>
@@ -1503,7 +1503,7 @@
         <v>16.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>22.2</v>
+        <v>30.1</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>13.6</v>
@@ -1549,7 +1549,7 @@
         <v>18.1</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>8.6</v>
@@ -1563,20 +1563,20 @@
       <c r="K13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="8" t="n">
+      <c r="L13" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="M13" s="8" t="n">
+      <c r="M13" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="N13" s="8" t="n">
+      <c r="N13" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="O13" s="8" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="P13" s="8" t="n">
-        <v>0.1</v>
+      <c r="O13" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q13" s="8" t="n">
         <v>23.8</v>
@@ -1648,19 +1648,19 @@
       <c r="K14" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="L14" s="8" t="n">
+      <c r="L14" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="M14" s="8" t="n">
+      <c r="M14" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="N14" s="8" t="n">
+      <c r="N14" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="O14" s="8" t="n">
-        <v>98.7</v>
-      </c>
-      <c r="P14" s="8" t="n">
+      <c r="O14" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="P14" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q14" s="8" t="n">
@@ -1718,14 +1718,14 @@
       <c r="F15" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="G15" s="8" t="n">
-        <v>12.6</v>
+      <c r="G15" s="3" t="n">
+        <v>22.6</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>10.7</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>21.4</v>
+        <v>2.4</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.2</v>
@@ -1736,10 +1736,10 @@
       <c r="L15" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="M15" s="8" t="n">
+      <c r="M15" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="N15" s="8" t="n">
+      <c r="N15" s="3" t="n">
         <v>15.9</v>
       </c>
       <c r="O15" s="3" t="n">
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>230.6</v>
+        <v>230</v>
       </c>
       <c r="D16" s="8" t="n">
         <v>127.2</v>
@@ -1821,7 +1821,7 @@
       <c r="L16" s="9" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="M16" s="8" t="n">
+      <c r="M16" s="9" t="n">
         <v>66.2</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1853,10 +1853,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>99.3</v>
+        <v>99.8</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>18.4</v>
@@ -1878,15 +1878,15 @@
         <v>461.4</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="E17" s="8" t="n">
         <v>13</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="G17" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="G17" s="8" t="n">
         <v>12.4</v>
       </c>
       <c r="H17" s="3" t="n">
@@ -1899,12 +1899,12 @@
         <v>2.7</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>11.8</v>
+        <v>2</v>
       </c>
       <c r="L17" s="9" t="n">
         <v>13.4</v>
       </c>
-      <c r="M17" s="8" t="n">
+      <c r="M17" s="9" t="n">
         <v>13.2</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2135.6</v>
+        <v>335.6</v>
       </c>
       <c r="D19" s="8" t="n">
         <v>25.7</v>
@@ -2075,7 +2075,7 @@
         <v>14.2</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>19.8</v>
+        <v>11.8</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>18.5</v>
@@ -2163,7 +2163,7 @@
         <v>12.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>19.2</v>
+        <v>1.4</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>184.4</v>
@@ -2241,14 +2241,14 @@
       <c r="K21" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="L21" s="8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="M21" s="8" t="n">
-        <v>16.5</v>
+      <c r="L21" s="13" t="n">
+        <v>-15.8</v>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>-15.8</v>
       </c>
       <c r="N21" s="8" t="n">
-        <v>18.7</v>
+        <v>1.8</v>
       </c>
       <c r="O21" s="8" t="n">
         <v>100</v>
@@ -2278,7 +2278,7 @@
         <v>16.4</v>
       </c>
       <c r="X21" s="8" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="Y21" s="8" t="n">
         <v>98</v>
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>508.9</v>
+        <v>50.8</v>
       </c>
       <c r="D22" s="8" t="n">
         <v>25.8</v>
@@ -2327,18 +2327,18 @@
         <v>5.7</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="O22" s="3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="M22" s="8" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="N22" s="8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="O22" s="8" t="n">
         <v>97</v>
       </c>
-      <c r="P22" s="3" t="n">
+      <c r="P22" s="8" t="n">
         <v>0.6</v>
       </c>
       <c r="Q22" s="8" t="n">
@@ -2411,7 +2411,7 @@
       <c r="K23" s="8" t="n">
         <v>27.4</v>
       </c>
-      <c r="L23" s="8" t="n">
+      <c r="L23" s="9" t="n">
         <v>70.7</v>
       </c>
       <c r="M23" s="9" t="n">
@@ -2494,7 +2494,7 @@
       <c r="K24" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L24" s="8" t="n">
+      <c r="L24" s="9" t="n">
         <v>14.1</v>
       </c>
       <c r="M24" s="9" t="n">
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>233.6</v>
+        <v>233.5</v>
       </c>
       <c r="D25" s="8" t="n">
         <v>23.1</v>
@@ -2576,22 +2576,22 @@
       <c r="J25" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="K25" s="8" t="n">
+      <c r="K25" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="L25" s="8" t="n">
-        <v>16.5</v>
+      <c r="L25" s="3" t="n">
+        <v>16</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="N25" s="8" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="O25" s="8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="O25" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P25" s="8" t="n">
+      <c r="P25" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q25" s="8" t="n">
@@ -2610,7 +2610,7 @@
         <v>1.5</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="W25" s="3" t="n">
         <v>17</v>
@@ -2649,8 +2649,8 @@
       <c r="F26" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="G26" s="3" t="n">
-        <v>71.2</v>
+      <c r="G26" s="8" t="n">
+        <v>7.1</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>13.2</v>
@@ -2661,17 +2661,17 @@
       <c r="J26" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="K26" s="8" t="n">
+      <c r="K26" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>9.9</v>
+        <v>15.8</v>
       </c>
       <c r="M26" s="8" t="n">
-        <v>9.9</v>
+        <v>15.8</v>
       </c>
       <c r="N26" s="8" t="n">
-        <v>12.2</v>
+        <v>17.9</v>
       </c>
       <c r="O26" s="8" t="n">
         <v>100</v>
@@ -2742,7 +2742,7 @@
       <c r="J27" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="K27" s="8" t="n">
+      <c r="K27" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="L27" s="8" t="n">
@@ -2782,7 +2782,7 @@
         <v>17.6</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>19.3</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>88</v>
@@ -2827,7 +2827,7 @@
       <c r="J28" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="K28" s="8" t="n">
+      <c r="K28" s="3" t="n">
         <v>32.8</v>
       </c>
       <c r="L28" s="3" t="n">
@@ -2860,20 +2860,20 @@
       <c r="U28" s="8" t="n">
         <v>3.4</v>
       </c>
-      <c r="V28" s="8" t="n">
+      <c r="V28" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="W28" s="8" t="n">
+      <c r="W28" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="X28" s="8" t="n">
+      <c r="X28" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="Y28" s="8" t="n">
+      <c r="Y28" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="Z28" s="8" t="n">
-        <v>0.4</v>
+      <c r="Z28" s="3" t="n">
+        <v>0.7</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2912,11 +2912,11 @@
       <c r="J29" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="K29" s="8" t="n">
-        <v>6.6</v>
+      <c r="K29" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>13.1</v>
+        <v>13.9</v>
       </c>
       <c r="M29" s="8" t="n">
         <v>15</v>
@@ -2977,7 +2977,7 @@
         <v>156.9</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>116.7</v>
+        <v>116.8</v>
       </c>
       <c r="E30" s="8" t="n">
         <v>71.90000000000001</v>
@@ -2997,13 +2997,13 @@
       <c r="J30" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="K30" s="8" t="n">
+      <c r="K30" s="9" t="n">
         <v>76.90000000000001</v>
       </c>
       <c r="L30" s="9" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="M30" s="9" t="n">
+      <c r="M30" s="8" t="n">
         <v>74.3</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -3020,7 +3020,7 @@
         <v>89.2</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>413.1</v>
@@ -3068,8 +3068,8 @@
       <c r="F31" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="G31" s="3" t="n">
-        <v>90.40000000000001</v>
+      <c r="G31" s="8" t="n">
+        <v>9</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>12.5</v>
@@ -3082,19 +3082,19 @@
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="M31" s="9" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="O31" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>20.1</v>
+        <v>-46</v>
+      </c>
+      <c r="M31" s="8" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="N31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P31" s="8" t="n">
+        <v>0.1</v>
       </c>
       <c r="Q31" s="8" t="n">
         <v>19.9</v>
@@ -3112,7 +3112,7 @@
         <v>2.9</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>170.4</v>
+        <v>170</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>16.3</v>
@@ -3143,13 +3143,13 @@
         <v>364.6</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="E32" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="G32" s="8" t="n">
         <v>14.3</v>
@@ -3161,41 +3161,37 @@
         <v>0.8</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>32.3</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q32" s="8" t="n">
+      <c r="Q32" s="3" t="n">
         <v>15</v>
       </c>
       <c r="R32" s="8" t="n">
         <v>14.8</v>
       </c>
-      <c r="S32" s="8" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v>98.7</v>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="U32" s="3" t="inlineStr"/>
       <c r="V32" s="8" t="n">
         <v>16.6</v>
       </c>
@@ -3310,18 +3306,18 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>211.4</v>
+        <v>21.1</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>19.7</v>
+        <v>21.7</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>15.1</v>
+        <v>13.1</v>
       </c>
       <c r="F34" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="G34" s="8" t="n">
+      <c r="G34" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="H34" s="3" t="n">
@@ -3339,32 +3335,32 @@
       <c r="L34" s="8" t="n">
         <v>15.1</v>
       </c>
-      <c r="M34" s="13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="N34" s="3" t="n">
+      <c r="M34" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="N34" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="O34" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="P34" s="3" t="n">
+      <c r="O34" s="8" t="n">
+        <v>99</v>
+      </c>
+      <c r="P34" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q34" s="8" t="n">
+      <c r="Q34" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="R34" s="8" t="n">
         <v>15.8</v>
       </c>
-      <c r="S34" s="8" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v>1.3</v>
+      <c r="S34" s="3" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="T34" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="U34" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="V34" s="8" t="n">
         <v>16.4</v>
@@ -3436,20 +3432,20 @@
       <c r="P35" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q35" s="8" t="n">
+      <c r="Q35" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="R35" s="8" t="n">
         <v>18.3</v>
       </c>
-      <c r="S35" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v>8.6</v>
+      <c r="S35" s="3" t="n">
+        <v>212.8</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="V35" s="8" t="n">
         <v>18.4</v>
@@ -3521,20 +3517,20 @@
       <c r="P36" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q36" s="8" t="n">
-        <v>24</v>
+      <c r="Q36" s="3" t="n">
+        <v>27</v>
       </c>
       <c r="R36" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="S36" s="8" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v>9.699999999999999</v>
+      <c r="S36" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>13.4</v>
       </c>
       <c r="V36" s="8" t="n">
         <v>20.8</v>
@@ -3565,19 +3561,19 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>207.8</v>
-      </c>
-      <c r="D37" s="8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D37" s="9" t="n">
         <v>118.4</v>
       </c>
-      <c r="E37" s="8" t="n">
+      <c r="E37" s="9" t="n">
         <v>66.09999999999999</v>
       </c>
       <c r="F37" s="8" t="n">
         <v>92.2</v>
       </c>
-      <c r="G37" s="3" t="n">
-        <v>32.3</v>
+      <c r="G37" s="8" t="n">
+        <v>52.3</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>56.7</v>
@@ -3604,9 +3600,9 @@
         <v>492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="Q37" s="8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q37" s="9" t="n">
         <v>101</v>
       </c>
       <c r="R37" s="9" t="n">
@@ -3616,7 +3612,7 @@
         <v>88.09999999999999</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>3809.1</v>
+        <v>380.9</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>33.2</v>
@@ -3650,10 +3646,10 @@
       <c r="C38" s="3" t="n">
         <v>415.6</v>
       </c>
-      <c r="D38" s="8" t="n">
+      <c r="D38" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="E38" s="8" t="n">
+      <c r="E38" s="9" t="n">
         <v>13.1</v>
       </c>
       <c r="F38" s="8" t="n">
@@ -3681,28 +3677,28 @@
         <v>13.5</v>
       </c>
       <c r="N38" s="8" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="O38" s="8" t="n">
-        <v>98.7</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="P38" s="8" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q38" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q38" s="9" t="n">
         <v>20.2</v>
       </c>
       <c r="R38" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="S38" s="8" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v>81.8</v>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v>4.3</v>
+      <c r="S38" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="T38" s="3" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>6.6</v>
       </c>
       <c r="V38" s="8" t="n">
         <v>18</v>
@@ -3769,13 +3765,13 @@
         <v>13.2</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q39" s="8" t="n">
-        <v>25.8</v>
+        <v>24.8</v>
       </c>
       <c r="R39" s="8" t="n">
         <v>18.4</v>
@@ -3784,10 +3780,10 @@
         <v>21.2</v>
       </c>
       <c r="T39" s="8" t="n">
-        <v>63.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="U39" s="8" t="n">
-        <v>12.1</v>
+        <v>10.1</v>
       </c>
       <c r="V39" s="8" t="n">
         <v>21.5</v>
@@ -3863,16 +3859,16 @@
         <v>25.4</v>
       </c>
       <c r="R40" s="8" t="n">
-        <v>17.6</v>
+        <v>13.8</v>
       </c>
       <c r="S40" s="8" t="n">
-        <v>20.1</v>
+        <v>15.8</v>
       </c>
       <c r="T40" s="8" t="n">
-        <v>62</v>
+        <v>48.8</v>
       </c>
       <c r="U40" s="8" t="n">
-        <v>12.3</v>
+        <v>16.7</v>
       </c>
       <c r="V40" s="8" t="n">
         <v>22.3</v>
@@ -3935,7 +3931,7 @@
         <v>12.3</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>0.4</v>
@@ -4102,7 +4098,7 @@
         <v>12.7</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>97</v>
@@ -4154,7 +4150,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="8" t="inlineStr"/>
       <c r="E44" s="8" t="inlineStr"/>
@@ -4170,7 +4166,7 @@
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
       <c r="Q44" s="8" t="inlineStr"/>
-      <c r="R44" s="8" t="inlineStr"/>
+      <c r="R44" s="14" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
@@ -4223,21 +4219,21 @@
         <v>56.4</v>
       </c>
       <c r="M45" s="9" t="n">
-        <v>55.9</v>
+        <v>55.4</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>26</v>
+        <v>490</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>2</v>
       </c>
       <c r="Q45" s="8" t="n">
-        <v>127.3</v>
-      </c>
-      <c r="R45" s="8" t="n">
+        <v>126.3</v>
+      </c>
+      <c r="R45" s="9" t="n">
         <v>89.2</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4256,7 +4252,7 @@
         <v>83.09999999999999</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>60.8</v>
+        <v>60</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>302.8</v>
@@ -4278,7 +4274,7 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>223.9</v>
+        <v>623.9</v>
       </c>
       <c r="D46" s="8" t="n">
         <v>26.2</v>
@@ -4302,13 +4298,13 @@
         <v>5.5</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="9" t="n">
         <v>11.3</v>
       </c>
       <c r="M46" s="9" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>13.1</v>
@@ -4322,7 +4318,7 @@
       <c r="Q46" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="R46" s="8" t="n">
+      <c r="R46" s="9" t="n">
         <v>17.8</v>
       </c>
       <c r="S46" s="8" t="n">

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_lastcheck.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_lastcheck.xlsx
@@ -820,13 +820,13 @@
         <v>17.3</v>
       </c>
       <c r="S4" s="8" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="T4" s="8" t="n">
-        <v>97.5</v>
+        <v>96.2</v>
       </c>
       <c r="U4" s="8" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="V4" s="8" t="n">
         <v>17.8</v>
@@ -835,13 +835,13 @@
         <v>17</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="Y4" s="8" t="n">
-        <v>95.09999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="Z4" s="8" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -890,19 +890,19 @@
         <v>13.9</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="O5" s="8" t="n">
-        <v>99.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P5" s="8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q5" s="8" t="n">
         <v>21.3</v>
       </c>
       <c r="R5" s="8" t="n">
-        <v>17.9</v>
+        <v>18.9</v>
       </c>
       <c r="S5" s="8" t="n">
         <v>20.5</v>
@@ -920,13 +920,13 @@
         <v>17.4</v>
       </c>
       <c r="X5" s="8" t="n">
-        <v>19.9</v>
+        <v>17.9</v>
       </c>
       <c r="Y5" s="8" t="n">
-        <v>83.40000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="Z5" s="8" t="n">
-        <v>3.9</v>
+        <v>5.9</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -975,19 +975,19 @@
         <v>14.2</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>99.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q6" s="8" t="n">
         <v>22.2</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>15.9</v>
+        <v>17.9</v>
       </c>
       <c r="S6" s="8" t="n">
         <v>18.1</v>
@@ -1005,13 +1005,13 @@
         <v>18</v>
       </c>
       <c r="X6" s="8" t="n">
-        <v>20.6</v>
+        <v>20.1</v>
       </c>
       <c r="Y6" s="8" t="n">
-        <v>95.09999999999999</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="Z6" s="8" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1060,13 +1060,13 @@
         <v>15.2</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>17.3</v>
+        <v>17.1</v>
       </c>
       <c r="O7" s="8" t="n">
-        <v>98.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P7" s="8" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="Q7" s="8" t="n">
         <v>20</v>
@@ -1075,19 +1075,19 @@
         <v>17.2</v>
       </c>
       <c r="S7" s="8" t="n">
-        <v>19.6</v>
+        <v>17.7</v>
       </c>
       <c r="T7" s="8" t="n">
-        <v>83.90000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="V7" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="W7" s="8" t="n">
-        <v>16.1</v>
+        <v>17</v>
       </c>
       <c r="X7" s="8" t="n">
         <v>18.3</v>
@@ -1157,7 +1157,7 @@
         <v>22.1</v>
       </c>
       <c r="R8" s="8" t="n">
-        <v>17.1</v>
+        <v>18.6</v>
       </c>
       <c r="S8" s="8" t="n">
         <v>19.5</v>
@@ -1175,13 +1175,13 @@
         <v>17.8</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>20.4</v>
+        <v>19</v>
       </c>
       <c r="Y8" s="8" t="n">
-        <v>88.2</v>
+        <v>82.3</v>
       </c>
       <c r="Z8" s="8" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
       <c r="Q9" s="8" t="n">
         <v>103.3</v>
       </c>
-      <c r="R9" s="9" t="n">
+      <c r="R9" s="8" t="n">
         <v>89.90000000000001</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1256,7 +1256,7 @@
       <c r="V9" s="8" t="n">
         <v>95.5</v>
       </c>
-      <c r="W9" s="9" t="n">
+      <c r="W9" s="8" t="n">
         <v>87.2</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1318,25 +1318,25 @@
         <v>16.9</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>99.40000000000001</v>
+        <v>99</v>
       </c>
       <c r="P10" s="8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q10" s="8" t="n">
         <v>20.7</v>
       </c>
-      <c r="R10" s="9" t="n">
+      <c r="R10" s="8" t="n">
         <v>18</v>
       </c>
       <c r="S10" s="8" t="n">
-        <v>20.6</v>
+        <v>18.8</v>
       </c>
       <c r="T10" s="8" t="n">
-        <v>84.5</v>
+        <v>77</v>
       </c>
       <c r="U10" s="8" t="n">
-        <v>3.8</v>
+        <v>5.6</v>
       </c>
       <c r="V10" s="8" t="n">
         <v>19.1</v>
@@ -1345,13 +1345,13 @@
         <v>17.4</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>19.9</v>
+        <v>18.7</v>
       </c>
       <c r="Y10" s="8" t="n">
-        <v>89.90000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1430,13 +1430,13 @@
         <v>18.1</v>
       </c>
       <c r="X11" s="8" t="n">
-        <v>20.8</v>
+        <v>20.4</v>
       </c>
       <c r="Y11" s="8" t="n">
-        <v>96.90000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="Z11" s="8" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>21.2</v>
       </c>
       <c r="W12" s="8" t="n">
-        <v>18.5</v>
+        <v>19.3</v>
       </c>
       <c r="X12" s="8" t="n">
         <v>21.3</v>
@@ -1581,8 +1581,8 @@
       <c r="Q13" s="8" t="n">
         <v>23.8</v>
       </c>
-      <c r="R13" s="8" t="n">
-        <v>17.3</v>
+      <c r="R13" s="3" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="S13" s="8" t="n">
         <v>19.7</v>
@@ -1600,13 +1600,13 @@
         <v>17.8</v>
       </c>
       <c r="X13" s="8" t="n">
-        <v>20.4</v>
+        <v>18.3</v>
       </c>
       <c r="Y13" s="8" t="n">
-        <v>83</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="Z13" s="8" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1685,13 +1685,13 @@
         <v>18.4</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>21.2</v>
+        <v>19.6</v>
       </c>
       <c r="Y14" s="8" t="n">
-        <v>87.2</v>
+        <v>81</v>
       </c>
       <c r="Z14" s="8" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1751,8 +1751,8 @@
       <c r="Q15" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="R15" s="8" t="n">
-        <v>13.9</v>
+      <c r="R15" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="S15" s="8" t="n">
         <v>15.9</v>
@@ -1770,13 +1770,13 @@
         <v>17.3</v>
       </c>
       <c r="X15" s="8" t="n">
-        <v>19.7</v>
+        <v>18.4</v>
       </c>
       <c r="Y15" s="8" t="n">
-        <v>88.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="Z15" s="8" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
       <c r="V16" s="8" t="n">
         <v>100.4</v>
       </c>
-      <c r="W16" s="9" t="n">
+      <c r="W16" s="8" t="n">
         <v>90.90000000000001</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1938,13 +1938,13 @@
         <v>18.2</v>
       </c>
       <c r="X17" s="8" t="n">
-        <v>20.9</v>
+        <v>19.6</v>
       </c>
       <c r="Y17" s="8" t="n">
-        <v>88.8</v>
+        <v>83.3</v>
       </c>
       <c r="Z17" s="8" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>22.4</v>
       </c>
       <c r="R18" s="8" t="n">
-        <v>17.6</v>
+        <v>19</v>
       </c>
       <c r="S18" s="8" t="n">
         <v>20.1</v>
@@ -2020,7 +2020,7 @@
         <v>20.2</v>
       </c>
       <c r="W18" s="8" t="n">
-        <v>14.1</v>
+        <v>16.7</v>
       </c>
       <c r="X18" s="8" t="n">
         <v>16.1</v>
@@ -2093,19 +2093,19 @@
         <v>18.2</v>
       </c>
       <c r="S19" s="8" t="n">
-        <v>20.9</v>
+        <v>16.6</v>
       </c>
       <c r="T19" s="8" t="n">
-        <v>67.90000000000001</v>
+        <v>54</v>
       </c>
       <c r="U19" s="8" t="n">
-        <v>9.9</v>
+        <v>14.2</v>
       </c>
       <c r="V19" s="8" t="n">
         <v>19.4</v>
       </c>
       <c r="W19" s="8" t="n">
-        <v>16.6</v>
+        <v>17.5</v>
       </c>
       <c r="X19" s="8" t="n">
         <v>18.9</v>
@@ -2159,16 +2159,16 @@
       <c r="L20" s="8" t="n">
         <v>12.6</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="8" t="n">
         <v>12.4</v>
       </c>
-      <c r="N20" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>184.4</v>
-      </c>
-      <c r="P20" s="3" t="n">
+      <c r="N20" s="8" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="P20" s="8" t="n">
         <v>0.4</v>
       </c>
       <c r="Q20" s="8" t="n">
@@ -2178,19 +2178,19 @@
         <v>17.5</v>
       </c>
       <c r="S20" s="8" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="T20" s="8" t="n">
-        <v>69.5</v>
+        <v>55.5</v>
       </c>
       <c r="U20" s="8" t="n">
-        <v>8.800000000000001</v>
+        <v>12.8</v>
       </c>
       <c r="V20" s="8" t="n">
         <v>19.2</v>
       </c>
       <c r="W20" s="8" t="n">
-        <v>17</v>
+        <v>17.7</v>
       </c>
       <c r="X20" s="8" t="n">
         <v>19.4</v>
@@ -2244,8 +2244,8 @@
       <c r="L21" s="13" t="n">
         <v>-15.8</v>
       </c>
-      <c r="M21" s="13" t="n">
-        <v>-15.8</v>
+      <c r="M21" s="3" t="n">
+        <v>16.5</v>
       </c>
       <c r="N21" s="8" t="n">
         <v>1.8</v>
@@ -2263,13 +2263,13 @@
         <v>18.1</v>
       </c>
       <c r="S21" s="8" t="n">
-        <v>20.8</v>
+        <v>19</v>
       </c>
       <c r="T21" s="8" t="n">
-        <v>85.09999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="U21" s="8" t="n">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="V21" s="8" t="n">
         <v>16.6</v>
@@ -2329,8 +2329,8 @@
       <c r="L22" s="8" t="n">
         <v>16.7</v>
       </c>
-      <c r="M22" s="8" t="n">
-        <v>16.2</v>
+      <c r="M22" s="3" t="n">
+        <v>12.9</v>
       </c>
       <c r="N22" s="8" t="n">
         <v>18.4</v>
@@ -2348,13 +2348,13 @@
         <v>18.7</v>
       </c>
       <c r="S22" s="8" t="n">
-        <v>21.6</v>
+        <v>17.5</v>
       </c>
       <c r="T22" s="8" t="n">
-        <v>69.7</v>
+        <v>56.7</v>
       </c>
       <c r="U22" s="8" t="n">
-        <v>9.4</v>
+        <v>13.4</v>
       </c>
       <c r="V22" s="8" t="n">
         <v>18.9</v>
@@ -2363,13 +2363,13 @@
         <v>18</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>20.6</v>
+        <v>20</v>
       </c>
       <c r="Y22" s="8" t="n">
-        <v>94.5</v>
+        <v>91.7</v>
       </c>
       <c r="Z22" s="8" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
       <c r="Q23" s="8" t="n">
         <v>115.6</v>
       </c>
-      <c r="R23" s="9" t="n">
+      <c r="R23" s="8" t="n">
         <v>91.5</v>
       </c>
       <c r="S23" s="3" t="inlineStr"/>
@@ -2442,7 +2442,7 @@
       <c r="V23" s="8" t="n">
         <v>94.3</v>
       </c>
-      <c r="W23" s="9" t="n">
+      <c r="W23" s="8" t="n">
         <v>86.3</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2512,32 +2512,32 @@
       <c r="Q24" s="8" t="n">
         <v>23.1</v>
       </c>
-      <c r="R24" s="9" t="n">
+      <c r="R24" s="8" t="n">
         <v>18.3</v>
       </c>
       <c r="S24" s="8" t="n">
-        <v>21</v>
+        <v>17.7</v>
       </c>
       <c r="T24" s="8" t="n">
-        <v>74.40000000000001</v>
+        <v>62.8</v>
       </c>
       <c r="U24" s="8" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="V24" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="W24" s="9" t="n">
+      <c r="W24" s="8" t="n">
         <v>17.3</v>
       </c>
       <c r="X24" s="8" t="n">
-        <v>19.7</v>
+        <v>18.6</v>
       </c>
       <c r="Y24" s="8" t="n">
-        <v>90.40000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="Z24" s="8" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2601,13 +2601,13 @@
         <v>17.2</v>
       </c>
       <c r="S25" s="8" t="n">
-        <v>19.6</v>
+        <v>18.8</v>
       </c>
       <c r="T25" s="8" t="n">
-        <v>92.7</v>
+        <v>88.8</v>
       </c>
       <c r="U25" s="8" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="V25" s="3" t="n">
         <v>17.3</v>
@@ -2686,13 +2686,13 @@
         <v>17.2</v>
       </c>
       <c r="S26" s="8" t="n">
-        <v>19.6</v>
+        <v>19.1</v>
       </c>
       <c r="T26" s="8" t="n">
-        <v>95.09999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="U26" s="8" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>15.6</v>
@@ -2764,7 +2764,7 @@
         <v>19.8</v>
       </c>
       <c r="R27" s="8" t="n">
-        <v>17.6</v>
+        <v>18.8</v>
       </c>
       <c r="S27" s="8" t="n">
         <v>20.1</v>
@@ -2852,13 +2852,13 @@
         <v>17</v>
       </c>
       <c r="S28" s="8" t="n">
-        <v>19.4</v>
+        <v>17.6</v>
       </c>
       <c r="T28" s="8" t="n">
-        <v>84.90000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="U28" s="8" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>17.2</v>
@@ -2934,7 +2934,7 @@
         <v>23.6</v>
       </c>
       <c r="R29" s="8" t="n">
-        <v>16.8</v>
+        <v>19</v>
       </c>
       <c r="S29" s="8" t="n">
         <v>19.1</v>
@@ -3016,7 +3016,7 @@
       <c r="Q30" s="8" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="R30" s="9" t="n">
+      <c r="R30" s="8" t="n">
         <v>89.2</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3099,17 +3099,17 @@
       <c r="Q31" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="R31" s="9" t="n">
+      <c r="R31" s="8" t="n">
         <v>17.8</v>
       </c>
       <c r="S31" s="8" t="n">
-        <v>20.4</v>
+        <v>18.9</v>
       </c>
       <c r="T31" s="8" t="n">
-        <v>87.7</v>
+        <v>81.5</v>
       </c>
       <c r="U31" s="8" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="V31" s="9" t="n">
         <v>170</v>
@@ -3199,13 +3199,13 @@
         <v>16.2</v>
       </c>
       <c r="X32" s="8" t="n">
-        <v>18.4</v>
+        <v>18.1</v>
       </c>
       <c r="Y32" s="8" t="n">
-        <v>97.5</v>
+        <v>96</v>
       </c>
       <c r="Z32" s="8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>21.2</v>
       </c>
       <c r="R33" s="8" t="n">
-        <v>17.2</v>
+        <v>18.4</v>
       </c>
       <c r="S33" s="8" t="n">
         <v>19.6</v>
@@ -3284,13 +3284,13 @@
         <v>16.5</v>
       </c>
       <c r="X33" s="8" t="n">
-        <v>18.8</v>
+        <v>17.9</v>
       </c>
       <c r="Y33" s="8" t="n">
-        <v>92.09999999999999</v>
+        <v>87.7</v>
       </c>
       <c r="Z33" s="8" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3342,24 +3342,24 @@
         <v>17</v>
       </c>
       <c r="O34" s="8" t="n">
-        <v>99</v>
+        <v>98.8</v>
       </c>
       <c r="P34" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q34" s="3" t="n">
+      <c r="Q34" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="R34" s="8" t="n">
         <v>15.8</v>
       </c>
-      <c r="S34" s="3" t="n">
+      <c r="S34" s="8" t="n">
         <v>17.3</v>
       </c>
-      <c r="T34" s="3" t="n">
+      <c r="T34" s="8" t="n">
         <v>90</v>
       </c>
-      <c r="U34" s="3" t="n">
+      <c r="U34" s="8" t="n">
         <v>2</v>
       </c>
       <c r="V34" s="8" t="n">
@@ -3369,13 +3369,13 @@
         <v>15.2</v>
       </c>
       <c r="X34" s="8" t="n">
-        <v>17.3</v>
+        <v>16.4</v>
       </c>
       <c r="Y34" s="8" t="n">
-        <v>92.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="Z34" s="8" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3420,16 +3420,16 @@
       <c r="L35" s="8" t="n">
         <v>12.5</v>
       </c>
-      <c r="M35" s="3" t="n">
+      <c r="M35" s="8" t="n">
         <v>12.3</v>
       </c>
-      <c r="N35" s="3" t="n">
+      <c r="N35" s="8" t="n">
         <v>14.1</v>
       </c>
-      <c r="O35" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P35" s="3" t="n">
+      <c r="O35" s="8" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="P35" s="8" t="n">
         <v>0.4</v>
       </c>
       <c r="Q35" s="3" t="n">
@@ -3451,7 +3451,7 @@
         <v>18.4</v>
       </c>
       <c r="W35" s="8" t="n">
-        <v>15.6</v>
+        <v>16.5</v>
       </c>
       <c r="X35" s="8" t="n">
         <v>17.7</v>
@@ -3539,13 +3539,13 @@
         <v>17.2</v>
       </c>
       <c r="X36" s="8" t="n">
-        <v>19.6</v>
+        <v>17.2</v>
       </c>
       <c r="Y36" s="8" t="n">
-        <v>79.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="Z36" s="8" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
       <c r="Q37" s="9" t="n">
         <v>101</v>
       </c>
-      <c r="R37" s="9" t="n">
+      <c r="R37" s="8" t="n">
         <v>84.90000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3620,7 +3620,7 @@
       <c r="V37" s="8" t="n">
         <v>90</v>
       </c>
-      <c r="W37" s="9" t="n">
+      <c r="W37" s="8" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3688,7 +3688,7 @@
       <c r="Q38" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="R38" s="9" t="n">
+      <c r="R38" s="8" t="n">
         <v>17</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3707,13 +3707,13 @@
         <v>16.3</v>
       </c>
       <c r="X38" s="8" t="n">
-        <v>18.5</v>
+        <v>17.4</v>
       </c>
       <c r="Y38" s="8" t="n">
-        <v>89.8</v>
+        <v>84.2</v>
       </c>
       <c r="Z38" s="8" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3777,13 +3777,13 @@
         <v>18.4</v>
       </c>
       <c r="S39" s="8" t="n">
-        <v>21.2</v>
+        <v>16.8</v>
       </c>
       <c r="T39" s="8" t="n">
-        <v>67.59999999999999</v>
+        <v>53.6</v>
       </c>
       <c r="U39" s="8" t="n">
-        <v>10.1</v>
+        <v>14.5</v>
       </c>
       <c r="V39" s="8" t="n">
         <v>21.5</v>
@@ -3792,13 +3792,13 @@
         <v>16.8</v>
       </c>
       <c r="X39" s="8" t="n">
-        <v>19.1</v>
+        <v>15.9</v>
       </c>
       <c r="Y39" s="8" t="n">
-        <v>74.59999999999999</v>
+        <v>62.1</v>
       </c>
       <c r="Z39" s="8" t="n">
-        <v>6.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>25.4</v>
       </c>
       <c r="R40" s="8" t="n">
-        <v>13.8</v>
+        <v>17.6</v>
       </c>
       <c r="S40" s="8" t="n">
         <v>15.8</v>
@@ -3877,13 +3877,13 @@
         <v>17.3</v>
       </c>
       <c r="X40" s="8" t="n">
-        <v>19.7</v>
+        <v>16.3</v>
       </c>
       <c r="Y40" s="8" t="n">
-        <v>73.3</v>
+        <v>60.6</v>
       </c>
       <c r="Z40" s="8" t="n">
-        <v>7.2</v>
+        <v>10.6</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3943,13 +3943,13 @@
         <v>17.2</v>
       </c>
       <c r="S41" s="8" t="n">
-        <v>19.6</v>
+        <v>14.2</v>
       </c>
       <c r="T41" s="8" t="n">
-        <v>61.2</v>
+        <v>44.2</v>
       </c>
       <c r="U41" s="8" t="n">
-        <v>12.4</v>
+        <v>17.9</v>
       </c>
       <c r="V41" s="8" t="n">
         <v>21.7</v>
@@ -3958,13 +3958,13 @@
         <v>16.2</v>
       </c>
       <c r="X41" s="8" t="n">
-        <v>18.4</v>
+        <v>14.7</v>
       </c>
       <c r="Y41" s="8" t="n">
-        <v>70.90000000000001</v>
+        <v>56.5</v>
       </c>
       <c r="Z41" s="8" t="n">
-        <v>7.5</v>
+        <v>11.3</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4028,13 +4028,13 @@
         <v>18.2</v>
       </c>
       <c r="S42" s="8" t="n">
-        <v>20.9</v>
+        <v>15.5</v>
       </c>
       <c r="T42" s="8" t="n">
-        <v>61.8</v>
+        <v>45.8</v>
       </c>
       <c r="U42" s="8" t="n">
-        <v>12.9</v>
+        <v>18.3</v>
       </c>
       <c r="V42" s="8" t="n">
         <v>22</v>
@@ -4043,13 +4043,13 @@
         <v>16.8</v>
       </c>
       <c r="X42" s="8" t="n">
-        <v>19.1</v>
+        <v>15.6</v>
       </c>
       <c r="Y42" s="8" t="n">
-        <v>72.3</v>
+        <v>58.9</v>
       </c>
       <c r="Z42" s="8" t="n">
-        <v>7.3</v>
+        <v>10.9</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4113,13 +4113,13 @@
         <v>17.8</v>
       </c>
       <c r="S43" s="8" t="n">
-        <v>20.4</v>
+        <v>15.6</v>
       </c>
       <c r="T43" s="8" t="n">
-        <v>65.09999999999999</v>
+        <v>49.8</v>
       </c>
       <c r="U43" s="8" t="n">
-        <v>10.9</v>
+        <v>15.7</v>
       </c>
       <c r="V43" s="8" t="n">
         <v>21.4</v>
@@ -4128,13 +4128,13 @@
         <v>16</v>
       </c>
       <c r="X43" s="8" t="n">
-        <v>18.2</v>
+        <v>14.5</v>
       </c>
       <c r="Y43" s="8" t="n">
-        <v>71.3</v>
+        <v>56.9</v>
       </c>
       <c r="Z43" s="8" t="n">
-        <v>7.3</v>
+        <v>11</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
       <c r="Q44" s="8" t="inlineStr"/>
-      <c r="R44" s="14" t="inlineStr"/>
+      <c r="R44" s="8" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
@@ -4233,7 +4233,7 @@
       <c r="Q45" s="8" t="n">
         <v>126.3</v>
       </c>
-      <c r="R45" s="9" t="n">
+      <c r="R45" s="8" t="n">
         <v>89.2</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4318,23 +4318,23 @@
       <c r="Q46" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="R46" s="9" t="n">
+      <c r="R46" s="8" t="n">
         <v>17.8</v>
       </c>
       <c r="S46" s="8" t="n">
-        <v>20.4</v>
+        <v>15.2</v>
       </c>
       <c r="T46" s="8" t="n">
-        <v>63.2</v>
+        <v>47.3</v>
       </c>
       <c r="U46" s="8" t="n">
-        <v>11.9</v>
+        <v>17</v>
       </c>
       <c r="V46" s="8" t="n">
         <v>21.8</v>
       </c>
       <c r="W46" s="8" t="n">
-        <v>14</v>
+        <v>16.6</v>
       </c>
       <c r="X46" s="8" t="n">
         <v>16</v>
